--- a/docs/stats.xlsx
+++ b/docs/stats.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcl\Desktop\misc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcl\OneDrive\Documents\GitHub\304-game\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8C12F81-31FB-419F-80E5-F982C39AECB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ECAA011-7714-4171-A505-716AB48E6431}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1800" yWindow="1180" windowWidth="28800" windowHeight="15370" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="19380" windowHeight="20970" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Revolutions" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="65">
   <si>
     <t>Date</t>
   </si>
@@ -247,6 +247,18 @@
   </si>
   <si>
     <t>Vithusayan Mokhanarajah</t>
+  </si>
+  <si>
+    <t>R20260403-1</t>
+  </si>
+  <si>
+    <t>R20260403-2</t>
+  </si>
+  <si>
+    <t>MN 250, PCC</t>
+  </si>
+  <si>
+    <t>Last row</t>
   </si>
 </sst>
 </file>
@@ -653,9 +665,29 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="525" row="2">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{8F285D60-1076-4165-80CE-C9172A156F72}">
+  <we:reference id="wa200009404" version="1.0.0.8" store="en-US" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="WA200009404" version="1.0.0.8" store="" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties/>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18.90625" customWidth="1"/>
@@ -816,7 +848,7 @@
         <v>0.85416666666666663</v>
       </c>
       <c r="E3" s="3">
-        <f t="shared" ref="E3:E24" si="1">MOD(D3 - C3, 1)</f>
+        <f t="shared" ref="E3:E26" si="1">MOD(D3 - C3, 1)</f>
         <v>0.16666666666666663</v>
       </c>
       <c r="F3" t="str" cm="1">
@@ -2959,6 +2991,196 @@
 )
 &amp;")"</f>
         <v>1 (23)</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>61</v>
+      </c>
+      <c r="B25" s="1">
+        <v>46115</v>
+      </c>
+      <c r="C25" s="2">
+        <v>0</v>
+      </c>
+      <c r="E25" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F25" t="str" cm="1">
+        <f t="array" ref="F25">COUNTIFS(
+ Matches!$A$2:$A$200,$A25,
+ Matches!$I$2:$I$200,"*"&amp;F$1&amp;"*"
+)
+&amp;" ("&amp;
+SUMPRODUCT(
+ (Matches!$A$2:$A$200=$A25) *
+ ((Matches!$C$2:$C$200=F$1)+(Matches!$D$2:$D$200=F$1)) *
+ Matches!$G$2:$G$200
+)
++
+SUMPRODUCT(
+ (Matches!$A$2:$A$200=$A25) *
+ ((Matches!$E$2:$E$200=F$1)+(Matches!$F$2:$F$200=F$1)) *
+ Matches!$H$2:$H$200
+)
+&amp;")"</f>
+        <v>2 (22)</v>
+      </c>
+      <c r="G25" t="str" cm="1">
+        <f t="array" ref="G25">COUNTIFS(
+ Matches!$A$2:$A$200,$A25,
+ Matches!$I$2:$I$200,"*"&amp;G$1&amp;"*"
+)
+&amp;" ("&amp;
+SUMPRODUCT(
+ (Matches!$A$2:$A$200=$A25) *
+ ((Matches!$C$2:$C$200=G$1)+(Matches!$D$2:$D$200=G$1)) *
+ Matches!$G$2:$G$200
+)
++
+SUMPRODUCT(
+ (Matches!$A$2:$A$200=$A25) *
+ ((Matches!$E$2:$E$200=G$1)+(Matches!$F$2:$F$200=G$1)) *
+ Matches!$H$2:$H$200
+)
+&amp;")"</f>
+        <v>0 (18)</v>
+      </c>
+      <c r="H25" t="str" cm="1">
+        <f t="array" ref="H25">COUNTIFS(
+ Matches!$A$2:$A$200,$A25,
+ Matches!$I$2:$I$200,"*"&amp;H$1&amp;"*"
+)
+&amp;" ("&amp;
+SUMPRODUCT(
+ (Matches!$A$2:$A$200=$A25) *
+ ((Matches!$C$2:$C$200=H$1)+(Matches!$D$2:$D$200=H$1)) *
+ Matches!$G$2:$G$200
+)
++
+SUMPRODUCT(
+ (Matches!$A$2:$A$200=$A25) *
+ ((Matches!$E$2:$E$200=H$1)+(Matches!$F$2:$F$200=H$1)) *
+ Matches!$H$2:$H$200
+)
+&amp;")"</f>
+        <v>2 (29)</v>
+      </c>
+      <c r="I25" t="str" cm="1">
+        <f t="array" ref="I25">COUNTIFS(
+ Matches!$A$2:$A$200,$A25,
+ Matches!$I$2:$I$200,"*"&amp;I$1&amp;"*"
+)
+&amp;" ("&amp;
+SUMPRODUCT(
+ (Matches!$A$2:$A$200=$A25) *
+ ((Matches!$C$2:$C$200=I$1)+(Matches!$D$2:$D$200=I$1)) *
+ Matches!$G$2:$G$200
+)
++
+SUMPRODUCT(
+ (Matches!$A$2:$A$200=$A25) *
+ ((Matches!$E$2:$E$200=I$1)+(Matches!$F$2:$F$200=I$1)) *
+ Matches!$H$2:$H$200
+)
+&amp;")"</f>
+        <v>2 (27)</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>62</v>
+      </c>
+      <c r="B26" s="1">
+        <v>46115</v>
+      </c>
+      <c r="C26" s="2">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="E26" s="3">
+        <f t="shared" si="1"/>
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="F26" t="str" cm="1">
+        <f t="array" ref="F26">COUNTIFS(
+ Matches!$A$2:$A$200,$A26,
+ Matches!$I$2:$I$200,"*"&amp;F$1&amp;"*"
+)
+&amp;" ("&amp;
+SUMPRODUCT(
+ (Matches!$A$2:$A$200=$A26) *
+ ((Matches!$C$2:$C$200=F$1)+(Matches!$D$2:$D$200=F$1)) *
+ Matches!$G$2:$G$200
+)
++
+SUMPRODUCT(
+ (Matches!$A$2:$A$200=$A26) *
+ ((Matches!$E$2:$E$200=F$1)+(Matches!$F$2:$F$200=F$1)) *
+ Matches!$H$2:$H$200
+)
+&amp;")"</f>
+        <v>1 (18)</v>
+      </c>
+      <c r="G26" t="str" cm="1">
+        <f t="array" ref="G26">COUNTIFS(
+ Matches!$A$2:$A$200,$A26,
+ Matches!$I$2:$I$200,"*"&amp;G$1&amp;"*"
+)
+&amp;" ("&amp;
+SUMPRODUCT(
+ (Matches!$A$2:$A$200=$A26) *
+ ((Matches!$C$2:$C$200=G$1)+(Matches!$D$2:$D$200=G$1)) *
+ Matches!$G$2:$G$200
+)
++
+SUMPRODUCT(
+ (Matches!$A$2:$A$200=$A26) *
+ ((Matches!$E$2:$E$200=G$1)+(Matches!$F$2:$F$200=G$1)) *
+ Matches!$H$2:$H$200
+)
+&amp;")"</f>
+        <v>1 (17)</v>
+      </c>
+      <c r="H26" t="str" cm="1">
+        <f t="array" ref="H26">COUNTIFS(
+ Matches!$A$2:$A$200,$A26,
+ Matches!$I$2:$I$200,"*"&amp;H$1&amp;"*"
+)
+&amp;" ("&amp;
+SUMPRODUCT(
+ (Matches!$A$2:$A$200=$A26) *
+ ((Matches!$C$2:$C$200=H$1)+(Matches!$D$2:$D$200=H$1)) *
+ Matches!$G$2:$G$200
+)
++
+SUMPRODUCT(
+ (Matches!$A$2:$A$200=$A26) *
+ ((Matches!$E$2:$E$200=H$1)+(Matches!$F$2:$F$200=H$1)) *
+ Matches!$H$2:$H$200
+)
+&amp;")"</f>
+        <v>3 (30)</v>
+      </c>
+      <c r="I26" t="str" cm="1">
+        <f t="array" ref="I26">COUNTIFS(
+ Matches!$A$2:$A$200,$A26,
+ Matches!$I$2:$I$200,"*"&amp;I$1&amp;"*"
+)
+&amp;" ("&amp;
+SUMPRODUCT(
+ (Matches!$A$2:$A$200=$A26) *
+ ((Matches!$C$2:$C$200=I$1)+(Matches!$D$2:$D$200=I$1)) *
+ Matches!$G$2:$G$200
+)
++
+SUMPRODUCT(
+ (Matches!$A$2:$A$200=$A26) *
+ ((Matches!$E$2:$E$200=I$1)+(Matches!$F$2:$F$200=I$1)) *
+ Matches!$H$2:$H$200
+)
+&amp;")"</f>
+        <v>1 (25)</v>
       </c>
     </row>
   </sheetData>
@@ -2993,7 +3215,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B6F95CC-DDBC-4D0D-92B0-0E6D3AF66C09}">
-  <dimension ref="A1:J69"/>
+  <dimension ref="A1:J75"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.90625" customWidth="1"/>
@@ -3098,7 +3320,7 @@
         <v>10</v>
       </c>
       <c r="I3" t="str">
-        <f t="shared" ref="I3:I69" si="0">IF(G3&gt;H3,
+        <f t="shared" ref="I3:I75" si="0">IF(G3&gt;H3,
    IF(C3&lt;D3, C3&amp;"/"&amp;D3, D3&amp;"/"&amp;C3),
    IF(E3&lt;F3, E3&amp;"/"&amp;F3, F3&amp;"/"&amp;E3)
 )</f>
@@ -5180,6 +5402,189 @@
       </c>
       <c r="J69" t="s">
         <v>57</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A70" t="s">
+        <v>61</v>
+      </c>
+      <c r="B70">
+        <v>1</v>
+      </c>
+      <c r="C70" t="s">
+        <v>15</v>
+      </c>
+      <c r="D70" t="s">
+        <v>14</v>
+      </c>
+      <c r="E70" t="s">
+        <v>12</v>
+      </c>
+      <c r="F70" t="s">
+        <v>13</v>
+      </c>
+      <c r="G70" s="4">
+        <v>9</v>
+      </c>
+      <c r="H70" s="4">
+        <v>10</v>
+      </c>
+      <c r="I70" t="str">
+        <f t="shared" si="0"/>
+        <v>LX/VM</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A71" t="s">
+        <v>61</v>
+      </c>
+      <c r="B71">
+        <v>2</v>
+      </c>
+      <c r="C71" t="s">
+        <v>15</v>
+      </c>
+      <c r="D71" t="s">
+        <v>13</v>
+      </c>
+      <c r="E71" t="s">
+        <v>12</v>
+      </c>
+      <c r="F71" t="s">
+        <v>14</v>
+      </c>
+      <c r="G71" s="4">
+        <v>7</v>
+      </c>
+      <c r="H71" s="4">
+        <v>10</v>
+      </c>
+      <c r="I71" t="str">
+        <f t="shared" si="0"/>
+        <v>LX/MN</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A72" t="s">
+        <v>61</v>
+      </c>
+      <c r="B72">
+        <v>3</v>
+      </c>
+      <c r="C72" t="s">
+        <v>12</v>
+      </c>
+      <c r="D72" t="s">
+        <v>15</v>
+      </c>
+      <c r="E72" t="s">
+        <v>14</v>
+      </c>
+      <c r="F72" t="s">
+        <v>13</v>
+      </c>
+      <c r="G72" s="4">
+        <v>2</v>
+      </c>
+      <c r="H72" s="4">
+        <v>10</v>
+      </c>
+      <c r="I72" t="str">
+        <f t="shared" si="0"/>
+        <v>MN/VM</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A73" t="s">
+        <v>62</v>
+      </c>
+      <c r="B73">
+        <v>1</v>
+      </c>
+      <c r="C73" t="s">
+        <v>15</v>
+      </c>
+      <c r="D73" t="s">
+        <v>13</v>
+      </c>
+      <c r="E73" t="s">
+        <v>14</v>
+      </c>
+      <c r="F73" t="s">
+        <v>12</v>
+      </c>
+      <c r="G73" s="4">
+        <v>7</v>
+      </c>
+      <c r="H73" s="4">
+        <v>10</v>
+      </c>
+      <c r="I73" t="str">
+        <f t="shared" si="0"/>
+        <v>LX/MN</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A74" t="s">
+        <v>62</v>
+      </c>
+      <c r="B74">
+        <v>2</v>
+      </c>
+      <c r="C74" t="s">
+        <v>12</v>
+      </c>
+      <c r="D74" t="s">
+        <v>13</v>
+      </c>
+      <c r="E74" t="s">
+        <v>15</v>
+      </c>
+      <c r="F74" t="s">
+        <v>14</v>
+      </c>
+      <c r="G74" s="4">
+        <v>8</v>
+      </c>
+      <c r="H74" s="4">
+        <v>10</v>
+      </c>
+      <c r="I74" t="str">
+        <f t="shared" si="0"/>
+        <v>ML/MN</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A75" t="s">
+        <v>62</v>
+      </c>
+      <c r="B75">
+        <v>3</v>
+      </c>
+      <c r="C75" t="s">
+        <v>12</v>
+      </c>
+      <c r="D75" t="s">
+        <v>15</v>
+      </c>
+      <c r="E75" t="s">
+        <v>14</v>
+      </c>
+      <c r="F75" t="s">
+        <v>13</v>
+      </c>
+      <c r="G75" s="4">
+        <v>0</v>
+      </c>
+      <c r="H75" s="4">
+        <v>10</v>
+      </c>
+      <c r="I75" t="str">
+        <f t="shared" si="0"/>
+        <v>MN/VM</v>
+      </c>
+      <c r="J75" t="s">
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -5208,7 +5613,7 @@
           <x14:formula1>
             <xm:f>Revolutions!$A:$A</xm:f>
           </x14:formula1>
-          <xm:sqref>A1:A1048576</xm:sqref>
+          <xm:sqref>A1:A69 A76:A1048576</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -5218,7 +5623,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32F4F995-3173-4CED-AE50-0BFB7C5A5258}">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="54.453125" customWidth="1"/>
@@ -5226,9 +5631,10 @@
     <col min="4" max="4" width="16.08984375" customWidth="1"/>
     <col min="5" max="5" width="15" customWidth="1"/>
     <col min="6" max="6" width="11.08984375" customWidth="1"/>
+    <col min="7" max="7" width="12.453125" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>41</v>
       </c>
@@ -5247,8 +5653,11 @@
       <c r="F1" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -5256,14 +5665,14 @@
         <v>43</v>
       </c>
       <c r="C2" cm="1">
-        <f t="array" ref="C2">SUMPRODUCT(
+        <f t="array" aca="1" ref="C2" ca="1">SUMPRODUCT(
   --(
-    (VALUE(LEFT(Revolutions!F2:F24,FIND(" ",Revolutions!F2:F24)-1)) =
-     _xlfn.BYROW(Revolutions!F2:I24,_xlfn.LAMBDA(_xlpm.r,MAX(VALUE(LEFT(_xlpm.r,FIND(" ",_xlpm.r)-1))))))
+    (VALUE(LEFT(INDIRECT("Revolutions!F2:F"&amp;$G$2),FIND(" ",INDIRECT("Revolutions!F2:F"&amp;$G$2))-1)) =
+     _xlfn.BYROW(INDIRECT("Revolutions!F2:I"&amp;$G$2),_xlfn.LAMBDA(_xlpm.r,MAX(VALUE(LEFT(_xlpm.r,FIND(" ",_xlpm.r)-1))))))
     *
-    (VALUE(MID(Revolutions!F2:F24,FIND("(",Revolutions!F2:F24)+1,
-      FIND(")",Revolutions!F2:F24)-FIND("(",Revolutions!F2:F24)-1)) =
-     _xlfn.BYROW(Revolutions!F2:I24,
+    (VALUE(MID(INDIRECT("Revolutions!F2:F"&amp;$G$2),FIND("(",INDIRECT("Revolutions!F2:F"&amp;$G$2))+1,
+      FIND(")",INDIRECT("Revolutions!F2:F"&amp;$G$2))-FIND("(",INDIRECT("Revolutions!F2:F"&amp;$G$2))-1)) =
+     _xlfn.BYROW(INDIRECT("Revolutions!F2:I"&amp;$G$2),
        _xlfn.LAMBDA(_xlpm.r,
          _xlfn.LET(
            _xlpm.m, VALUE(LEFT(_xlpm.r,FIND(" ",_xlpm.r)-1)),
@@ -5278,16 +5687,16 @@
         <v>6</v>
       </c>
       <c r="D2" cm="1">
-        <f t="array" ref="D2">SUMPRODUCT(--LEFT(Revolutions!F2:F24,1))</f>
-        <v>35</v>
+        <f t="array" aca="1" ref="D2" ca="1">SUMPRODUCT(--LEFT(INDIRECT("Revolutions!F2:F"&amp;$G$2)))</f>
+        <v>38</v>
       </c>
       <c r="E2" cm="1">
-        <f t="array" ref="E2">SUMPRODUCT(--MID(Revolutions!F2:F24, FIND("(",Revolutions!F2:F24)+1, LEN(Revolutions!F2:F24)-FIND("(",Revolutions!F2:F24)-1))</f>
-        <v>516</v>
+        <f t="array" aca="1" ref="E2" ca="1">SUMPRODUCT(--MID(INDIRECT("Revolutions!F2:F"&amp;$G$2), FIND("(",INDIRECT("Revolutions!F2:F"&amp;$G$2))+1, LEN(INDIRECT("Revolutions!F2:F"&amp;$G$2))-FIND("(",INDIRECT("Revolutions!F2:F"&amp;$G$2))-1))</f>
+        <v>556</v>
       </c>
       <c r="F2" cm="1">
-        <f t="array" ref="F2">SUM(
- _xlfn.BYROW(Revolutions!F2:I24,
+        <f t="array" aca="1" ref="F2" ca="1">SUM(
+ _xlfn.BYROW(INDIRECT("Revolutions!F2:I"&amp;$G$2),
   _xlfn.LAMBDA(_xlpm.r,
    _xlfn.LET(
     _xlpm.vals,VALUE(LEFT(_xlpm.r,FIND(" ",_xlpm.r)-1))*1000+
@@ -5299,10 +5708,14 @@
   )
  )
 )</f>
-        <v>60</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+        <v>64</v>
+      </c>
+      <c r="G2" cm="1">
+        <f t="array" ref="G2">MATCH(2,1/(Revolutions!A:A&lt;&gt;""),1)</f>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -5310,14 +5723,14 @@
         <v>58</v>
       </c>
       <c r="C3" cm="1">
-        <f t="array" ref="C3">SUMPRODUCT(
+        <f t="array" aca="1" ref="C3" ca="1">SUMPRODUCT(
  --(
-  (VALUE(LEFT(Revolutions!G2:G24,FIND(" ",Revolutions!G2:G24)-1))=
-   _xlfn.BYROW(Revolutions!F2:I24,_xlfn.LAMBDA(_xlpm.r,MAX(VALUE(LEFT(_xlpm.r,FIND(" ",_xlpm.r)-1))))))
+  (VALUE(LEFT(INDIRECT("Revolutions!G2:G"&amp;$G$2),FIND(" ",INDIRECT("Revolutions!G2:G"&amp;$G$2))-1))=
+   _xlfn.BYROW(INDIRECT("Revolutions!F2:I"&amp;$G$2),_xlfn.LAMBDA(_xlpm.r,MAX(VALUE(LEFT(_xlpm.r,FIND(" ",_xlpm.r)-1))))))
  *
-  (VALUE(MID(Revolutions!G2:G24,FIND("(",Revolutions!G2:G24)+1,
-   FIND(")",Revolutions!G2:G24)-FIND("(",Revolutions!G2:G24)-1))=
-   _xlfn.BYROW(Revolutions!F2:I24,
+  (VALUE(MID(INDIRECT("Revolutions!G2:G"&amp;$G$2),FIND("(",INDIRECT("Revolutions!G2:G"&amp;$G$2))+1,
+   FIND(")",INDIRECT("Revolutions!G2:G"&amp;$G$2))-FIND("(",INDIRECT("Revolutions!G2:G"&amp;$G$2))-1))=
+   _xlfn.BYROW(INDIRECT("Revolutions!F2:I"&amp;$G$2),
     _xlfn.LAMBDA(_xlpm.r,
      _xlfn.LET(
       _xlpm.m,VALUE(LEFT(_xlpm.r,FIND(" ",_xlpm.r)-1)),
@@ -5332,16 +5745,16 @@
         <v>7</v>
       </c>
       <c r="D3" cm="1">
-        <f t="array" ref="D3">SUMPRODUCT(--LEFT(Revolutions!G2:G24,1))</f>
-        <v>40</v>
+        <f t="array" aca="1" ref="D3" ca="1">SUMPRODUCT(--LEFT(INDIRECT("Revolutions!G2:G"&amp;$G$2),1))</f>
+        <v>41</v>
       </c>
       <c r="E3" cm="1">
-        <f t="array" ref="E3">SUMPRODUCT(--MID(Revolutions!G2:G24, FIND("(",Revolutions!G2:G24)+1, LEN(Revolutions!G2:G24)-FIND("(",Revolutions!G2:G24)-1))</f>
-        <v>524</v>
+        <f t="array" aca="1" ref="E3" ca="1">SUMPRODUCT(--MID(INDIRECT("Revolutions!G2:G"&amp;$G$2), FIND("(",INDIRECT("Revolutions!G2:G"&amp;$G$2))+1, LEN(INDIRECT("Revolutions!G2:G"&amp;$G$2))-FIND("(",INDIRECT("Revolutions!G2:G"&amp;$G$2))-1))</f>
+        <v>559</v>
       </c>
       <c r="F3" cm="1">
-        <f t="array" ref="F3">SUM(
- _xlfn.BYROW(Revolutions!F2:I24,
+        <f t="array" aca="1" ref="F3" ca="1">SUM(
+ _xlfn.BYROW(INDIRECT("Revolutions!F2:I"&amp;$G$2),
   _xlfn.LAMBDA(_xlpm.r,
    _xlfn.LET(
     _xlpm.vals,VALUE(LEFT(_xlpm.r,FIND(" ",_xlpm.r)-1))*1000+
@@ -5353,10 +5766,10 @@
   )
  )
 )</f>
-        <v>61</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -5364,14 +5777,14 @@
         <v>59</v>
       </c>
       <c r="C4" cm="1">
-        <f t="array" ref="C4">SUMPRODUCT(
+        <f t="array" aca="1" ref="C4" ca="1">SUMPRODUCT(
  --(
-  (VALUE(LEFT(Revolutions!H2:H24,FIND(" ",Revolutions!H2:H24)-1))=
-   _xlfn.BYROW(Revolutions!F2:I24,_xlfn.LAMBDA(_xlpm.r,MAX(VALUE(LEFT(_xlpm.r,FIND(" ",_xlpm.r)-1))))))
+  (VALUE(LEFT(INDIRECT("Revolutions!H2:H"&amp;$G$2),FIND(" ",INDIRECT("Revolutions!H2:H"&amp;$G$2))-1))=
+   _xlfn.BYROW(INDIRECT("Revolutions!F2:I"&amp;$G$2),_xlfn.LAMBDA(_xlpm.r,MAX(VALUE(LEFT(_xlpm.r,FIND(" ",_xlpm.r)-1))))))
  *
-  (VALUE(MID(Revolutions!H2:H24,FIND("(",Revolutions!H2:H24)+1,
-   FIND(")",Revolutions!H2:H24)-FIND("(",Revolutions!H2:H24)-1))=
-   _xlfn.BYROW(Revolutions!F2:I24,
+  (VALUE(MID(INDIRECT("Revolutions!H2:H"&amp;$G$2),FIND("(",INDIRECT("Revolutions!H2:H"&amp;$G$2))+1,
+   FIND(")",INDIRECT("Revolutions!H2:H"&amp;$G$2))-FIND("(",INDIRECT("Revolutions!H2:H"&amp;$G$2))-1))=
+   _xlfn.BYROW(INDIRECT("Revolutions!F2:I"&amp;$G$2),
     _xlfn.LAMBDA(_xlpm.r,
      _xlfn.LET(
       _xlpm.m,VALUE(LEFT(_xlpm.r,FIND(" ",_xlpm.r)-1)),
@@ -5383,19 +5796,19 @@
   )
  )
 )</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D4" cm="1">
-        <f t="array" ref="D4">SUMPRODUCT(--LEFT(Revolutions!H2:H24,1))</f>
-        <v>36</v>
+        <f t="array" aca="1" ref="D4" ca="1">SUMPRODUCT(--LEFT(INDIRECT("Revolutions!H2:H"&amp;$G$2)))</f>
+        <v>41</v>
       </c>
       <c r="E4" cm="1">
-        <f t="array" ref="E4">SUMPRODUCT(--MID(Revolutions!H2:H24, FIND("(",Revolutions!H2:H24)+1, LEN(Revolutions!H2:H24)-FIND("(",Revolutions!H2:H24)-1))</f>
-        <v>538</v>
+        <f t="array" aca="1" ref="E4" ca="1">SUMPRODUCT(--MID(INDIRECT("Revolutions!H2:H"&amp;$G$2), FIND("(",INDIRECT("Revolutions!H2:H"&amp;$G$2))+1, LEN(INDIRECT("Revolutions!H2:H"&amp;$G$2))-FIND("(",INDIRECT("Revolutions!H2:H"&amp;$G$2))-1))</f>
+        <v>597</v>
       </c>
       <c r="F4" cm="1">
-        <f t="array" ref="F4">SUM(
- _xlfn.BYROW(Revolutions!F2:I24,
+        <f t="array" aca="1" ref="F4" ca="1">SUM(
+ _xlfn.BYROW(INDIRECT("Revolutions!F2:I"&amp;$G$2),
   _xlfn.LAMBDA(_xlpm.r,
    _xlfn.LET(
     _xlpm.vals,VALUE(LEFT(_xlpm.r,FIND(" ",_xlpm.r)-1))*1000+
@@ -5407,10 +5820,10 @@
   )
  )
 )</f>
-        <v>64</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -5418,14 +5831,14 @@
         <v>60</v>
       </c>
       <c r="C5" cm="1">
-        <f t="array" ref="C5">SUMPRODUCT(
+        <f t="array" aca="1" ref="C5" ca="1">SUMPRODUCT(
  --(
-  (VALUE(LEFT(Revolutions!I2:I24,FIND(" ",Revolutions!I2:I24)-1))=
-   _xlfn.BYROW(Revolutions!F2:I24,_xlfn.LAMBDA(_xlpm.r,MAX(VALUE(LEFT(_xlpm.r,FIND(" ",_xlpm.r)-1))))))
+  (VALUE(LEFT(INDIRECT("Revolutions!I2:I"&amp;$G$2),FIND(" ",INDIRECT("Revolutions!I2:I"&amp;$G$2))-1))=
+   _xlfn.BYROW(INDIRECT("Revolutions!F2:I"&amp;$G$2),_xlfn.LAMBDA(_xlpm.r,MAX(VALUE(LEFT(_xlpm.r,FIND(" ",_xlpm.r)-1))))))
  *
-  (VALUE(MID(Revolutions!I2:I24,FIND("(",Revolutions!I2:I24)+1,
-   FIND(")",Revolutions!I2:I24)-FIND("(",Revolutions!I2:I24)-1))=
-   _xlfn.BYROW(Revolutions!F2:I24,
+  (VALUE(MID(INDIRECT("Revolutions!I2:I"&amp;$G$2),FIND("(",INDIRECT("Revolutions!I2:I"&amp;$G$2))+1,
+   FIND(")",INDIRECT("Revolutions!I2:I"&amp;$G$2))-FIND("(",INDIRECT("Revolutions!I2:I"&amp;$G$2))-1))=
+   _xlfn.BYROW(INDIRECT("Revolutions!F2:I"&amp;$G$2),
     _xlfn.LAMBDA(_xlpm.r,
      _xlfn.LET(
       _xlpm.m,VALUE(LEFT(_xlpm.r,FIND(" ",_xlpm.r)-1)),
@@ -5440,16 +5853,16 @@
         <v>5</v>
       </c>
       <c r="D5" cm="1">
-        <f t="array" ref="D5">SUMPRODUCT(--LEFT(Revolutions!I2:I24,1))</f>
-        <v>25</v>
+        <f t="array" aca="1" ref="D5" ca="1">SUMPRODUCT(--LEFT(INDIRECT("Revolutions!I2:I"&amp;$G$2),1))</f>
+        <v>28</v>
       </c>
       <c r="E5" cm="1">
-        <f t="array" ref="E5">SUMPRODUCT(--MID(Revolutions!I2:I24, FIND("(",Revolutions!I2:I24)+1, LEN(Revolutions!I2:I24)-FIND("(",Revolutions!I2:I24)-1))</f>
-        <v>482</v>
+        <f t="array" aca="1" ref="E5" ca="1">SUMPRODUCT(--MID(INDIRECT("Revolutions!I2:I"&amp;$G$2), FIND("(",INDIRECT("Revolutions!I2:I"&amp;$G$2))+1, LEN(INDIRECT("Revolutions!I2:I"&amp;$G$2))-FIND("(",INDIRECT("Revolutions!I2:I"&amp;$G$2))-1))</f>
+        <v>534</v>
       </c>
       <c r="F5" cm="1">
-        <f t="array" ref="F5">SUM(
- _xlfn.BYROW(Revolutions!F2:I24,
+        <f t="array" aca="1" ref="F5" ca="1">SUM(
+ _xlfn.BYROW(INDIRECT("Revolutions!F2:I"&amp;$G$2),
   _xlfn.LAMBDA(_xlpm.r,
    _xlfn.LET(
     _xlpm.vals,VALUE(LEFT(_xlpm.r,FIND(" ",_xlpm.r)-1))*1000+
@@ -5461,7 +5874,7 @@
   )
  )
 )</f>
-        <v>54</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>

--- a/docs/stats.xlsx
+++ b/docs/stats.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcl\OneDrive\Documents\GitHub\304-game\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl$\Ubuntu\home\marc\GitHub\304-game\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ECAA011-7714-4171-A505-716AB48E6431}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEE32CB1-E036-44A3-81F0-DFF98C5F582F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="19380" windowHeight="20970" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Revolutions" sheetId="1" r:id="rId1"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="68">
   <si>
     <t>Date</t>
   </si>
@@ -259,6 +259,15 @@
   </si>
   <si>
     <t>Last row</t>
+  </si>
+  <si>
+    <t>R20260406-1</t>
+  </si>
+  <si>
+    <t>R20260406-2</t>
+  </si>
+  <si>
+    <t>250 CAPS</t>
   </si>
 </sst>
 </file>
@@ -687,7 +696,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:J28"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18.90625" customWidth="1"/>
@@ -848,7 +857,7 @@
         <v>0.85416666666666663</v>
       </c>
       <c r="E3" s="3">
-        <f t="shared" ref="E3:E26" si="1">MOD(D3 - C3, 1)</f>
+        <f t="shared" ref="E3:E28" si="1">MOD(D3 - C3, 1)</f>
         <v>0.16666666666666663</v>
       </c>
       <c r="F3" t="str" cm="1">
@@ -2416,7 +2425,7 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19" t="str">
-        <f t="shared" ref="A19:A24" si="2">"R"&amp;TEXT(B19,"yyyymmdd")&amp;"-"&amp;COUNTIFS($B:$B,B19,$C:$C,"&lt;="&amp;C19)</f>
+        <f t="shared" ref="A19:A28" si="2">"R"&amp;TEXT(B19,"yyyymmdd")&amp;"-"&amp;COUNTIFS($B:$B,B19,$C:$C,"&lt;="&amp;C19)</f>
         <v>R20260216-2</v>
       </c>
       <c r="B19" s="1">
@@ -2707,7 +2716,7 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A22" t="str">
-        <f t="shared" si="2"/>
+        <f>"R"&amp;TEXT(B22,"yyyymmdd")&amp;"-"&amp;COUNTIFS($B:$B,B22,$C:$C,"&lt;="&amp;C22)</f>
         <v>R20260318-1</v>
       </c>
       <c r="B22" s="1">
@@ -3181,6 +3190,198 @@
 )
 &amp;")"</f>
         <v>1 (25)</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A27" t="str">
+        <f>"R"&amp;TEXT(B27,"yyyymmdd")&amp;"-"&amp;COUNTIFS($B:$B,B27,$C:$C,"&lt;="&amp;C27)</f>
+        <v>R20260406-1</v>
+      </c>
+      <c r="B27" s="1">
+        <v>46118</v>
+      </c>
+      <c r="C27" s="2">
+        <v>0</v>
+      </c>
+      <c r="E27" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F27" t="str" cm="1">
+        <f t="array" ref="F27">COUNTIFS(
+ Matches!$A$2:$A$200,$A27,
+ Matches!$I$2:$I$200,"*"&amp;F$1&amp;"*"
+)
+&amp;" ("&amp;
+SUMPRODUCT(
+ (Matches!$A$2:$A$200=$A27) *
+ ((Matches!$C$2:$C$200=F$1)+(Matches!$D$2:$D$200=F$1)) *
+ Matches!$G$2:$G$200
+)
++
+SUMPRODUCT(
+ (Matches!$A$2:$A$200=$A27) *
+ ((Matches!$E$2:$E$200=F$1)+(Matches!$F$2:$F$200=F$1)) *
+ Matches!$H$2:$H$200
+)
+&amp;")"</f>
+        <v>2 (21)</v>
+      </c>
+      <c r="G27" t="str" cm="1">
+        <f t="array" ref="G27">COUNTIFS(
+ Matches!$A$2:$A$200,$A27,
+ Matches!$I$2:$I$200,"*"&amp;G$1&amp;"*"
+)
+&amp;" ("&amp;
+SUMPRODUCT(
+ (Matches!$A$2:$A$200=$A27) *
+ ((Matches!$C$2:$C$200=G$1)+(Matches!$D$2:$D$200=G$1)) *
+ Matches!$G$2:$G$200
+)
++
+SUMPRODUCT(
+ (Matches!$A$2:$A$200=$A27) *
+ ((Matches!$E$2:$E$200=G$1)+(Matches!$F$2:$F$200=G$1)) *
+ Matches!$H$2:$H$200
+)
+&amp;")"</f>
+        <v>0 (15)</v>
+      </c>
+      <c r="H27" t="str" cm="1">
+        <f t="array" ref="H27">COUNTIFS(
+ Matches!$A$2:$A$200,$A27,
+ Matches!$I$2:$I$200,"*"&amp;H$1&amp;"*"
+)
+&amp;" ("&amp;
+SUMPRODUCT(
+ (Matches!$A$2:$A$200=$A27) *
+ ((Matches!$C$2:$C$200=H$1)+(Matches!$D$2:$D$200=H$1)) *
+ Matches!$G$2:$G$200
+)
++
+SUMPRODUCT(
+ (Matches!$A$2:$A$200=$A27) *
+ ((Matches!$E$2:$E$200=H$1)+(Matches!$F$2:$F$200=H$1)) *
+ Matches!$H$2:$H$200
+)
+&amp;")"</f>
+        <v>2 (29)</v>
+      </c>
+      <c r="I27" t="str" cm="1">
+        <f t="array" ref="I27">COUNTIFS(
+ Matches!$A$2:$A$200,$A27,
+ Matches!$I$2:$I$200,"*"&amp;I$1&amp;"*"
+)
+&amp;" ("&amp;
+SUMPRODUCT(
+ (Matches!$A$2:$A$200=$A27) *
+ ((Matches!$C$2:$C$200=I$1)+(Matches!$D$2:$D$200=I$1)) *
+ Matches!$G$2:$G$200
+)
++
+SUMPRODUCT(
+ (Matches!$A$2:$A$200=$A27) *
+ ((Matches!$E$2:$E$200=I$1)+(Matches!$F$2:$F$200=I$1)) *
+ Matches!$H$2:$H$200
+)
+&amp;")"</f>
+        <v>2 (25)</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A28" t="str">
+        <f>"R"&amp;TEXT(B28,"yyyymmdd")&amp;"-"&amp;COUNTIFS($B:$B,B28,$C:$C,"&lt;="&amp;C28)</f>
+        <v>R20260406-2</v>
+      </c>
+      <c r="B28" s="1">
+        <v>46118</v>
+      </c>
+      <c r="C28" s="2">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="E28" s="3">
+        <f t="shared" si="1"/>
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="F28" t="str" cm="1">
+        <f t="array" ref="F28">COUNTIFS(
+ Matches!$A$2:$A$200,$A28,
+ Matches!$I$2:$I$200,"*"&amp;F$1&amp;"*"
+)
+&amp;" ("&amp;
+SUMPRODUCT(
+ (Matches!$A$2:$A$200=$A28) *
+ ((Matches!$C$2:$C$200=F$1)+(Matches!$D$2:$D$200=F$1)) *
+ Matches!$G$2:$G$200
+)
++
+SUMPRODUCT(
+ (Matches!$A$2:$A$200=$A28) *
+ ((Matches!$E$2:$E$200=F$1)+(Matches!$F$2:$F$200=F$1)) *
+ Matches!$H$2:$H$200
+)
+&amp;")"</f>
+        <v>2 (24)</v>
+      </c>
+      <c r="G28" t="str" cm="1">
+        <f t="array" ref="G28">COUNTIFS(
+ Matches!$A$2:$A$200,$A28,
+ Matches!$I$2:$I$200,"*"&amp;G$1&amp;"*"
+)
+&amp;" ("&amp;
+SUMPRODUCT(
+ (Matches!$A$2:$A$200=$A28) *
+ ((Matches!$C$2:$C$200=G$1)+(Matches!$D$2:$D$200=G$1)) *
+ Matches!$G$2:$G$200
+)
++
+SUMPRODUCT(
+ (Matches!$A$2:$A$200=$A28) *
+ ((Matches!$E$2:$E$200=G$1)+(Matches!$F$2:$F$200=G$1)) *
+ Matches!$H$2:$H$200
+)
+&amp;")"</f>
+        <v>2 (21)</v>
+      </c>
+      <c r="H28" t="str" cm="1">
+        <f t="array" ref="H28">COUNTIFS(
+ Matches!$A$2:$A$200,$A28,
+ Matches!$I$2:$I$200,"*"&amp;H$1&amp;"*"
+)
+&amp;" ("&amp;
+SUMPRODUCT(
+ (Matches!$A$2:$A$200=$A28) *
+ ((Matches!$C$2:$C$200=H$1)+(Matches!$D$2:$D$200=H$1)) *
+ Matches!$G$2:$G$200
+)
++
+SUMPRODUCT(
+ (Matches!$A$2:$A$200=$A28) *
+ ((Matches!$E$2:$E$200=H$1)+(Matches!$F$2:$F$200=H$1)) *
+ Matches!$H$2:$H$200
+)
+&amp;")"</f>
+        <v>0 (14)</v>
+      </c>
+      <c r="I28" t="str" cm="1">
+        <f t="array" ref="I28">COUNTIFS(
+ Matches!$A$2:$A$200,$A28,
+ Matches!$I$2:$I$200,"*"&amp;I$1&amp;"*"
+)
+&amp;" ("&amp;
+SUMPRODUCT(
+ (Matches!$A$2:$A$200=$A28) *
+ ((Matches!$C$2:$C$200=I$1)+(Matches!$D$2:$D$200=I$1)) *
+ Matches!$G$2:$G$200
+)
++
+SUMPRODUCT(
+ (Matches!$A$2:$A$200=$A28) *
+ ((Matches!$E$2:$E$200=I$1)+(Matches!$F$2:$F$200=I$1)) *
+ Matches!$H$2:$H$200
+)
+&amp;")"</f>
+        <v>2 (29)</v>
       </c>
     </row>
   </sheetData>
@@ -3215,7 +3416,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B6F95CC-DDBC-4D0D-92B0-0E6D3AF66C09}">
-  <dimension ref="A1:J75"/>
+  <dimension ref="A1:J81"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.90625" customWidth="1"/>
@@ -3320,7 +3521,7 @@
         <v>10</v>
       </c>
       <c r="I3" t="str">
-        <f t="shared" ref="I3:I75" si="0">IF(G3&gt;H3,
+        <f t="shared" ref="I3:I81" si="0">IF(G3&gt;H3,
    IF(C3&lt;D3, C3&amp;"/"&amp;D3, D3&amp;"/"&amp;C3),
    IF(E3&lt;F3, E3&amp;"/"&amp;F3, F3&amp;"/"&amp;E3)
 )</f>
@@ -5585,6 +5786,189 @@
       </c>
       <c r="J75" t="s">
         <v>63</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A76" t="s">
+        <v>65</v>
+      </c>
+      <c r="B76">
+        <v>1</v>
+      </c>
+      <c r="C76" t="s">
+        <v>15</v>
+      </c>
+      <c r="D76" t="s">
+        <v>14</v>
+      </c>
+      <c r="E76" t="s">
+        <v>12</v>
+      </c>
+      <c r="F76" t="s">
+        <v>13</v>
+      </c>
+      <c r="G76" s="4">
+        <v>9</v>
+      </c>
+      <c r="H76" s="4">
+        <v>10</v>
+      </c>
+      <c r="I76" t="str">
+        <f t="shared" si="0"/>
+        <v>LX/VM</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A77" t="s">
+        <v>65</v>
+      </c>
+      <c r="B77">
+        <v>2</v>
+      </c>
+      <c r="C77" t="s">
+        <v>15</v>
+      </c>
+      <c r="D77" t="s">
+        <v>13</v>
+      </c>
+      <c r="E77" t="s">
+        <v>14</v>
+      </c>
+      <c r="F77" t="s">
+        <v>12</v>
+      </c>
+      <c r="G77" s="4">
+        <v>5</v>
+      </c>
+      <c r="H77" s="4">
+        <v>10</v>
+      </c>
+      <c r="I77" t="str">
+        <f t="shared" si="0"/>
+        <v>LX/MN</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A78" t="s">
+        <v>65</v>
+      </c>
+      <c r="B78">
+        <v>3</v>
+      </c>
+      <c r="C78" t="s">
+        <v>15</v>
+      </c>
+      <c r="D78" t="s">
+        <v>12</v>
+      </c>
+      <c r="E78" t="s">
+        <v>14</v>
+      </c>
+      <c r="F78" t="s">
+        <v>13</v>
+      </c>
+      <c r="G78" s="4">
+        <v>1</v>
+      </c>
+      <c r="H78" s="4">
+        <v>10</v>
+      </c>
+      <c r="I78" t="str">
+        <f t="shared" si="0"/>
+        <v>MN/VM</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A79" t="s">
+        <v>66</v>
+      </c>
+      <c r="B79">
+        <v>1</v>
+      </c>
+      <c r="C79" t="s">
+        <v>14</v>
+      </c>
+      <c r="D79" t="s">
+        <v>12</v>
+      </c>
+      <c r="E79" t="s">
+        <v>13</v>
+      </c>
+      <c r="F79" t="s">
+        <v>15</v>
+      </c>
+      <c r="G79" s="4">
+        <v>4</v>
+      </c>
+      <c r="H79" s="4">
+        <v>10</v>
+      </c>
+      <c r="I79" t="str">
+        <f t="shared" si="0"/>
+        <v>ML/VM</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A80" t="s">
+        <v>66</v>
+      </c>
+      <c r="B80">
+        <v>2</v>
+      </c>
+      <c r="C80" t="s">
+        <v>15</v>
+      </c>
+      <c r="D80" t="s">
+        <v>14</v>
+      </c>
+      <c r="E80" t="s">
+        <v>13</v>
+      </c>
+      <c r="F80" t="s">
+        <v>12</v>
+      </c>
+      <c r="G80" s="4">
+        <v>1</v>
+      </c>
+      <c r="H80" s="4">
+        <v>10</v>
+      </c>
+      <c r="I80" t="str">
+        <f t="shared" si="0"/>
+        <v>LX/VM</v>
+      </c>
+      <c r="J80" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A81" t="s">
+        <v>66</v>
+      </c>
+      <c r="B81">
+        <v>3</v>
+      </c>
+      <c r="C81" t="s">
+        <v>13</v>
+      </c>
+      <c r="D81" t="s">
+        <v>14</v>
+      </c>
+      <c r="E81" t="s">
+        <v>15</v>
+      </c>
+      <c r="F81" t="s">
+        <v>12</v>
+      </c>
+      <c r="G81" s="4">
+        <v>9</v>
+      </c>
+      <c r="H81" s="4">
+        <v>10</v>
+      </c>
+      <c r="I81" t="str">
+        <f t="shared" si="0"/>
+        <v>LX/ML</v>
       </c>
     </row>
   </sheetData>
@@ -5613,7 +5997,7 @@
           <x14:formula1>
             <xm:f>Revolutions!$A:$A</xm:f>
           </x14:formula1>
-          <xm:sqref>A1:A69 A76:A1048576</xm:sqref>
+          <xm:sqref>A1:A69 A82:A1048576</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -5630,7 +6014,7 @@
     <col min="3" max="3" width="16.1796875" customWidth="1"/>
     <col min="4" max="4" width="16.08984375" customWidth="1"/>
     <col min="5" max="5" width="15" customWidth="1"/>
-    <col min="6" max="6" width="11.08984375" customWidth="1"/>
+    <col min="6" max="6" width="11.1796875" customWidth="1"/>
     <col min="7" max="7" width="12.453125" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5688,11 +6072,11 @@
       </c>
       <c r="D2" cm="1">
         <f t="array" aca="1" ref="D2" ca="1">SUMPRODUCT(--LEFT(INDIRECT("Revolutions!F2:F"&amp;$G$2)))</f>
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E2" cm="1">
         <f t="array" aca="1" ref="E2" ca="1">SUMPRODUCT(--MID(INDIRECT("Revolutions!F2:F"&amp;$G$2), FIND("(",INDIRECT("Revolutions!F2:F"&amp;$G$2))+1, LEN(INDIRECT("Revolutions!F2:F"&amp;$G$2))-FIND("(",INDIRECT("Revolutions!F2:F"&amp;$G$2))-1))</f>
-        <v>556</v>
+        <v>601</v>
       </c>
       <c r="F2" cm="1">
         <f t="array" aca="1" ref="F2" ca="1">SUM(
@@ -5708,11 +6092,11 @@
   )
  )
 )</f>
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="G2" cm="1">
         <f t="array" ref="G2">MATCH(2,1/(Revolutions!A:A&lt;&gt;""),1)</f>
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
@@ -5746,11 +6130,11 @@
       </c>
       <c r="D3" cm="1">
         <f t="array" aca="1" ref="D3" ca="1">SUMPRODUCT(--LEFT(INDIRECT("Revolutions!G2:G"&amp;$G$2),1))</f>
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E3" cm="1">
         <f t="array" aca="1" ref="E3" ca="1">SUMPRODUCT(--MID(INDIRECT("Revolutions!G2:G"&amp;$G$2), FIND("(",INDIRECT("Revolutions!G2:G"&amp;$G$2))+1, LEN(INDIRECT("Revolutions!G2:G"&amp;$G$2))-FIND("(",INDIRECT("Revolutions!G2:G"&amp;$G$2))-1))</f>
-        <v>559</v>
+        <v>595</v>
       </c>
       <c r="F3" cm="1">
         <f t="array" aca="1" ref="F3" ca="1">SUM(
@@ -5766,7 +6150,7 @@
   )
  )
 )</f>
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
@@ -5796,15 +6180,15 @@
   )
  )
 )</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" cm="1">
         <f t="array" aca="1" ref="D4" ca="1">SUMPRODUCT(--LEFT(INDIRECT("Revolutions!H2:H"&amp;$G$2)))</f>
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E4" cm="1">
         <f t="array" aca="1" ref="E4" ca="1">SUMPRODUCT(--MID(INDIRECT("Revolutions!H2:H"&amp;$G$2), FIND("(",INDIRECT("Revolutions!H2:H"&amp;$G$2))+1, LEN(INDIRECT("Revolutions!H2:H"&amp;$G$2))-FIND("(",INDIRECT("Revolutions!H2:H"&amp;$G$2))-1))</f>
-        <v>597</v>
+        <v>640</v>
       </c>
       <c r="F4" cm="1">
         <f t="array" aca="1" ref="F4" ca="1">SUM(
@@ -5820,7 +6204,7 @@
   )
  )
 )</f>
-        <v>72</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
@@ -5850,15 +6234,15 @@
   )
  )
 )</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D5" cm="1">
         <f t="array" aca="1" ref="D5" ca="1">SUMPRODUCT(--LEFT(INDIRECT("Revolutions!I2:I"&amp;$G$2),1))</f>
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E5" cm="1">
         <f t="array" aca="1" ref="E5" ca="1">SUMPRODUCT(--MID(INDIRECT("Revolutions!I2:I"&amp;$G$2), FIND("(",INDIRECT("Revolutions!I2:I"&amp;$G$2))+1, LEN(INDIRECT("Revolutions!I2:I"&amp;$G$2))-FIND("(",INDIRECT("Revolutions!I2:I"&amp;$G$2))-1))</f>
-        <v>534</v>
+        <v>588</v>
       </c>
       <c r="F5" cm="1">
         <f t="array" aca="1" ref="F5" ca="1">SUM(
@@ -5874,7 +6258,7 @@
   )
  )
 )</f>
-        <v>60</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>

--- a/docs/stats.xlsx
+++ b/docs/stats.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl$\Ubuntu\home\marc\GitHub\304-game\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEE32CB1-E036-44A3-81F0-DFF98C5F582F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F2ED69B-B1C8-4191-A81E-6286911A3BF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="11370" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Revolutions" sheetId="1" r:id="rId1"/>
     <sheet name="Matches" sheetId="3" r:id="rId2"/>
-    <sheet name="By Player" sheetId="4" r:id="rId3"/>
+    <sheet name="Betting" sheetId="5" r:id="rId3"/>
+    <sheet name="By Player" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="Initials">'By Player'!$A$2:$A$5</definedName>
@@ -64,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="812" uniqueCount="98">
   <si>
     <t>Date</t>
   </si>
@@ -268,6 +269,96 @@
   </si>
   <si>
     <t>250 CAPS</t>
+  </si>
+  <si>
+    <t>SetID</t>
+  </si>
+  <si>
+    <t>Win</t>
+  </si>
+  <si>
+    <t>seq</t>
+  </si>
+  <si>
+    <t>player</t>
+  </si>
+  <si>
+    <t>bet_tier</t>
+  </si>
+  <si>
+    <t>outcome</t>
+  </si>
+  <si>
+    <t>caps</t>
+  </si>
+  <si>
+    <t>stone_bonus</t>
+  </si>
+  <si>
+    <t>stones_delta</t>
+  </si>
+  <si>
+    <t>R20260318-1-1</t>
+  </si>
+  <si>
+    <t>2/3</t>
+  </si>
+  <si>
+    <t>1/2</t>
+  </si>
+  <si>
+    <t>penalty</t>
+  </si>
+  <si>
+    <t>W</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>R20260318-1-2</t>
+  </si>
+  <si>
+    <t>R20260318-1-3</t>
+  </si>
+  <si>
+    <t>notes</t>
+  </si>
+  <si>
+    <t>3/4</t>
+  </si>
+  <si>
+    <t>Late</t>
+  </si>
+  <si>
+    <t>V2 late caps on Lewei</t>
+  </si>
+  <si>
+    <t>R20260318-2-1</t>
+  </si>
+  <si>
+    <t>R20260318-2-2</t>
+  </si>
+  <si>
+    <t>R20260318-2-3</t>
+  </si>
+  <si>
+    <t>R20260318-3-1</t>
+  </si>
+  <si>
+    <t>R20260318-3-2</t>
+  </si>
+  <si>
+    <t>R20260303-3-1</t>
+  </si>
+  <si>
+    <t>Wrong</t>
+  </si>
+  <si>
+    <t>R20260303-3-2</t>
+  </si>
+  <si>
+    <t>R20260303-3-3</t>
   </si>
 </sst>
 </file>
@@ -312,12 +403,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2425,7 +2517,7 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19" t="str">
-        <f t="shared" ref="A19:A28" si="2">"R"&amp;TEXT(B19,"yyyymmdd")&amp;"-"&amp;COUNTIFS($B:$B,B19,$C:$C,"&lt;="&amp;C19)</f>
+        <f t="shared" ref="A19:A24" si="2">"R"&amp;TEXT(B19,"yyyymmdd")&amp;"-"&amp;COUNTIFS($B:$B,B19,$C:$C,"&lt;="&amp;C19)</f>
         <v>R20260216-2</v>
       </c>
       <c r="B19" s="1">
@@ -3416,7 +3508,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B6F95CC-DDBC-4D0D-92B0-0E6D3AF66C09}">
-  <dimension ref="A1:J81"/>
+  <dimension ref="A1:K81"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.90625" customWidth="1"/>
@@ -3426,9 +3518,11 @@
     <col min="5" max="5" width="10.453125" customWidth="1"/>
     <col min="6" max="6" width="10.08984375" customWidth="1"/>
     <col min="7" max="8" width="8.7265625" style="4"/>
+    <col min="10" max="10" width="29.7265625" customWidth="1"/>
+    <col min="11" max="11" width="14.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>17</v>
       </c>
@@ -3459,8 +3553,11 @@
       <c r="J1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -3493,8 +3590,12 @@
 )</f>
         <v>ML/MN</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K2" t="str">
+        <f>_xlfn.CONCAT(A2, "-", B2)</f>
+        <v>R20251201-1-1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -3527,8 +3628,12 @@
 )</f>
         <v>LX/MN</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K3" t="str">
+        <f t="shared" ref="K3:K66" si="1">_xlfn.CONCAT(A3, "-", B3)</f>
+        <v>R20251201-1-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -3558,8 +3663,12 @@
         <f t="shared" si="0"/>
         <v>LX/ML</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K4" t="str">
+        <f t="shared" si="1"/>
+        <v>R20251201-1-3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -3589,8 +3698,12 @@
         <f t="shared" si="0"/>
         <v>LX/ML</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K5" t="str">
+        <f t="shared" si="1"/>
+        <v>R20251215-1-1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -3620,8 +3733,12 @@
         <f t="shared" si="0"/>
         <v>ML/MN</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K6" t="str">
+        <f t="shared" si="1"/>
+        <v>R20251215-1-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -3651,8 +3768,12 @@
         <f t="shared" si="0"/>
         <v>ML/VM</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K7" t="str">
+        <f t="shared" si="1"/>
+        <v>R20251215-1-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>20</v>
       </c>
@@ -3682,8 +3803,12 @@
         <f t="shared" si="0"/>
         <v>ML/VM</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K8" t="str">
+        <f t="shared" si="1"/>
+        <v>R20251229-1-1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>20</v>
       </c>
@@ -3713,8 +3838,12 @@
         <f t="shared" si="0"/>
         <v>MN/VM</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K9" t="str">
+        <f t="shared" si="1"/>
+        <v>R20251229-1-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>20</v>
       </c>
@@ -3744,8 +3873,12 @@
         <f t="shared" si="0"/>
         <v>ML/MN</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K10" t="str">
+        <f t="shared" si="1"/>
+        <v>R20251229-1-3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>21</v>
       </c>
@@ -3775,8 +3908,12 @@
         <f t="shared" si="0"/>
         <v>ML/MN</v>
       </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K11" t="str">
+        <f t="shared" si="1"/>
+        <v>R20251229-2-1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>21</v>
       </c>
@@ -3806,8 +3943,12 @@
         <f t="shared" si="0"/>
         <v>LX/ML</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K12" t="str">
+        <f t="shared" si="1"/>
+        <v>R20251229-2-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -3837,8 +3978,12 @@
         <f t="shared" si="0"/>
         <v>LX/MN</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K13" t="str">
+        <f t="shared" si="1"/>
+        <v>R20251229-2-3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>22</v>
       </c>
@@ -3868,8 +4013,12 @@
         <f t="shared" si="0"/>
         <v>ML/MN</v>
       </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K14" t="str">
+        <f t="shared" si="1"/>
+        <v>R20260105-1-1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>22</v>
       </c>
@@ -3899,8 +4048,12 @@
         <f t="shared" si="0"/>
         <v>LX/ML</v>
       </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K15" t="str">
+        <f t="shared" si="1"/>
+        <v>R20260105-1-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>22</v>
       </c>
@@ -3930,8 +4083,12 @@
         <f t="shared" si="0"/>
         <v>LX/MN</v>
       </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K16" t="str">
+        <f t="shared" si="1"/>
+        <v>R20260105-1-3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>23</v>
       </c>
@@ -3961,8 +4118,12 @@
         <f t="shared" si="0"/>
         <v>LX/MN</v>
       </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K17" t="str">
+        <f t="shared" si="1"/>
+        <v>R20260105-2-1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>23</v>
       </c>
@@ -3992,8 +4153,12 @@
         <f t="shared" si="0"/>
         <v>LX/VM</v>
       </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K18" t="str">
+        <f t="shared" si="1"/>
+        <v>R20260105-2-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>23</v>
       </c>
@@ -4023,8 +4188,12 @@
         <f t="shared" si="0"/>
         <v>MN/VM</v>
       </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K19" t="str">
+        <f t="shared" si="1"/>
+        <v>R20260105-2-3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>24</v>
       </c>
@@ -4054,8 +4223,12 @@
         <f t="shared" si="0"/>
         <v>LX/MN</v>
       </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K20" t="str">
+        <f t="shared" si="1"/>
+        <v>R20260112-1-1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>24</v>
       </c>
@@ -4085,8 +4258,12 @@
         <f t="shared" si="0"/>
         <v>LX/ML</v>
       </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K21" t="str">
+        <f t="shared" si="1"/>
+        <v>R20260112-1-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>24</v>
       </c>
@@ -4116,8 +4293,12 @@
         <f t="shared" si="0"/>
         <v>ML/MN</v>
       </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K22" t="str">
+        <f t="shared" si="1"/>
+        <v>R20260112-1-3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>25</v>
       </c>
@@ -4147,8 +4328,12 @@
         <f t="shared" si="0"/>
         <v>LX/MN</v>
       </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K23" t="str">
+        <f t="shared" si="1"/>
+        <v>R20260112-2-1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>25</v>
       </c>
@@ -4178,8 +4363,12 @@
         <f t="shared" si="0"/>
         <v>ML/MN</v>
       </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K24" t="str">
+        <f t="shared" si="1"/>
+        <v>R20260112-2-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>25</v>
       </c>
@@ -4209,8 +4398,12 @@
         <f t="shared" si="0"/>
         <v>LX/ML</v>
       </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K25" t="str">
+        <f t="shared" si="1"/>
+        <v>R20260112-2-3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>26</v>
       </c>
@@ -4243,8 +4436,12 @@
       <c r="J26" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K26" t="str">
+        <f t="shared" si="1"/>
+        <v>R20260119-1-1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>26</v>
       </c>
@@ -4277,8 +4474,12 @@
       <c r="J27" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K27" t="str">
+        <f t="shared" si="1"/>
+        <v>R20260119-1-2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>26</v>
       </c>
@@ -4311,8 +4512,12 @@
       <c r="J28" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K28" t="str">
+        <f t="shared" si="1"/>
+        <v>R20260119-1-3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>27</v>
       </c>
@@ -4345,8 +4550,12 @@
       <c r="J29" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K29" t="str">
+        <f t="shared" si="1"/>
+        <v>R20260119-2-1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>27</v>
       </c>
@@ -4379,8 +4588,12 @@
       <c r="J30" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K30" t="str">
+        <f t="shared" si="1"/>
+        <v>R20260119-2-2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>27</v>
       </c>
@@ -4413,8 +4626,12 @@
       <c r="J31" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K31" t="str">
+        <f t="shared" si="1"/>
+        <v>R20260119-2-3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>28</v>
       </c>
@@ -4447,8 +4664,12 @@
       <c r="J32" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K32" t="str">
+        <f t="shared" si="1"/>
+        <v>R20260127-1-1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>28</v>
       </c>
@@ -4481,8 +4702,12 @@
       <c r="J33" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K33" t="str">
+        <f t="shared" si="1"/>
+        <v>R20260127-1-2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>28</v>
       </c>
@@ -4515,8 +4740,12 @@
       <c r="J34" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K34" t="str">
+        <f t="shared" si="1"/>
+        <v>R20260127-1-3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>29</v>
       </c>
@@ -4549,8 +4778,12 @@
       <c r="J35" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K35" t="str">
+        <f t="shared" si="1"/>
+        <v>R20260127-2-1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>29</v>
       </c>
@@ -4583,8 +4816,12 @@
       <c r="J36" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K36" t="str">
+        <f t="shared" si="1"/>
+        <v>R20260127-2-2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>29</v>
       </c>
@@ -4617,8 +4854,12 @@
       <c r="J37" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K37" t="str">
+        <f t="shared" si="1"/>
+        <v>R20260127-2-3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>30</v>
       </c>
@@ -4651,8 +4892,12 @@
       <c r="J38" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K38" t="str">
+        <f t="shared" si="1"/>
+        <v>R20260127-3-1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>30</v>
       </c>
@@ -4685,8 +4930,12 @@
       <c r="J39" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K39" t="str">
+        <f t="shared" si="1"/>
+        <v>R20260127-3-2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>30</v>
       </c>
@@ -4719,8 +4968,12 @@
       <c r="J40" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K40" t="str">
+        <f t="shared" si="1"/>
+        <v>R20260127-3-3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>31</v>
       </c>
@@ -4750,8 +5003,12 @@
         <f t="shared" si="0"/>
         <v>LX/ML</v>
       </c>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K41" t="str">
+        <f t="shared" si="1"/>
+        <v>R20260203-1-1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>31</v>
       </c>
@@ -4781,8 +5038,12 @@
         <f t="shared" si="0"/>
         <v>LX/VM</v>
       </c>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K42" t="str">
+        <f t="shared" si="1"/>
+        <v>R20260203-1-2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>31</v>
       </c>
@@ -4812,8 +5073,12 @@
         <f t="shared" si="0"/>
         <v>ML/VM</v>
       </c>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K43" t="str">
+        <f t="shared" si="1"/>
+        <v>R20260203-1-3</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>32</v>
       </c>
@@ -4843,8 +5108,12 @@
         <f t="shared" si="0"/>
         <v>LX/MN</v>
       </c>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K44" t="str">
+        <f t="shared" si="1"/>
+        <v>R20260203-2-1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>32</v>
       </c>
@@ -4874,8 +5143,12 @@
         <f t="shared" si="0"/>
         <v>MN/VM</v>
       </c>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K45" t="str">
+        <f t="shared" si="1"/>
+        <v>R20260203-2-2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>32</v>
       </c>
@@ -4905,8 +5178,12 @@
         <f t="shared" si="0"/>
         <v>ML/MN</v>
       </c>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K46" t="str">
+        <f t="shared" si="1"/>
+        <v>R20260203-2-3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>33</v>
       </c>
@@ -4936,8 +5213,12 @@
         <f t="shared" si="0"/>
         <v>LX/ML</v>
       </c>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K47" t="str">
+        <f t="shared" si="1"/>
+        <v>R20260203-3-1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>33</v>
       </c>
@@ -4967,8 +5248,12 @@
         <f t="shared" si="0"/>
         <v>LX/VM</v>
       </c>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="K48" t="str">
+        <f t="shared" si="1"/>
+        <v>R20260203-3-2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>33</v>
       </c>
@@ -4998,8 +5283,12 @@
         <f t="shared" si="0"/>
         <v>LX/MN</v>
       </c>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="K49" t="str">
+        <f t="shared" si="1"/>
+        <v>R20260203-3-3</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>48</v>
       </c>
@@ -5028,8 +5317,12 @@
         <f t="shared" si="0"/>
         <v>LX/MN</v>
       </c>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="K50" t="str">
+        <f t="shared" si="1"/>
+        <v>R20260216-1-1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>48</v>
       </c>
@@ -5058,8 +5351,12 @@
         <f t="shared" si="0"/>
         <v>LX/ML</v>
       </c>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="K51" t="str">
+        <f t="shared" si="1"/>
+        <v>R20260216-1-2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>48</v>
       </c>
@@ -5088,8 +5385,12 @@
         <f t="shared" si="0"/>
         <v>LX/VM</v>
       </c>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="K52" t="str">
+        <f t="shared" si="1"/>
+        <v>R20260216-1-3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>49</v>
       </c>
@@ -5118,8 +5419,12 @@
         <f t="shared" si="0"/>
         <v>ML/VM</v>
       </c>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="K53" t="str">
+        <f t="shared" si="1"/>
+        <v>R20260216-2-1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>49</v>
       </c>
@@ -5148,8 +5453,12 @@
         <f t="shared" si="0"/>
         <v>MN/VM</v>
       </c>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="K54" t="str">
+        <f t="shared" si="1"/>
+        <v>R20260216-2-2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>49</v>
       </c>
@@ -5178,8 +5487,12 @@
         <f t="shared" si="0"/>
         <v>LX/VM</v>
       </c>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="K55" t="str">
+        <f t="shared" si="1"/>
+        <v>R20260216-2-3</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>50</v>
       </c>
@@ -5208,8 +5521,12 @@
         <f t="shared" si="0"/>
         <v>ML/VM</v>
       </c>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="K56" t="str">
+        <f t="shared" si="1"/>
+        <v>R20260216-3-1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>50</v>
       </c>
@@ -5238,8 +5555,12 @@
         <f t="shared" si="0"/>
         <v>MN/VM</v>
       </c>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="K57" t="str">
+        <f t="shared" si="1"/>
+        <v>R20260216-3-2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>52</v>
       </c>
@@ -5268,8 +5589,12 @@
         <f t="shared" si="0"/>
         <v>ML/VM</v>
       </c>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="K58" t="str">
+        <f t="shared" si="1"/>
+        <v>R20260312-1-1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>52</v>
       </c>
@@ -5298,8 +5623,12 @@
         <f t="shared" si="0"/>
         <v>ML/MN</v>
       </c>
-    </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="K59" t="str">
+        <f t="shared" si="1"/>
+        <v>R20260312-1-2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>52</v>
       </c>
@@ -5328,8 +5657,12 @@
         <f t="shared" si="0"/>
         <v>MN/VM</v>
       </c>
-    </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="K60" t="str">
+        <f t="shared" si="1"/>
+        <v>R20260312-1-3</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>53</v>
       </c>
@@ -5358,8 +5691,12 @@
         <f t="shared" si="0"/>
         <v>ML/VM</v>
       </c>
-    </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="K61" t="str">
+        <f t="shared" si="1"/>
+        <v>R20260318-1-1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>53</v>
       </c>
@@ -5388,8 +5725,12 @@
         <f t="shared" si="0"/>
         <v>ML/MN</v>
       </c>
-    </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="K62" t="str">
+        <f t="shared" si="1"/>
+        <v>R20260318-1-2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>53</v>
       </c>
@@ -5418,8 +5759,12 @@
         <f t="shared" si="0"/>
         <v>LX/ML</v>
       </c>
-    </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="K63" t="str">
+        <f t="shared" si="1"/>
+        <v>R20260318-1-3</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>54</v>
       </c>
@@ -5448,8 +5793,12 @@
         <f t="shared" si="0"/>
         <v>LX/ML</v>
       </c>
-    </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K64" t="str">
+        <f t="shared" si="1"/>
+        <v>R20260318-2-1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>54</v>
       </c>
@@ -5478,8 +5827,12 @@
         <f t="shared" si="0"/>
         <v>ML/VM</v>
       </c>
-    </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K65" t="str">
+        <f t="shared" si="1"/>
+        <v>R20260318-2-2</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>54</v>
       </c>
@@ -5508,8 +5861,12 @@
         <f t="shared" si="0"/>
         <v>ML/MN</v>
       </c>
-    </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K66" t="str">
+        <f t="shared" si="1"/>
+        <v>R20260318-2-3</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>55</v>
       </c>
@@ -5538,8 +5895,12 @@
         <f t="shared" si="0"/>
         <v>ML/MN</v>
       </c>
-    </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K67" t="str">
+        <f t="shared" ref="K67:K81" si="2">_xlfn.CONCAT(A67, "-", B67)</f>
+        <v>R20260318-3-1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>55</v>
       </c>
@@ -5571,8 +5932,12 @@
       <c r="J68" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K68" t="str">
+        <f t="shared" si="2"/>
+        <v>R20260318-3-2</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>55</v>
       </c>
@@ -5604,8 +5969,12 @@
       <c r="J69" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K69" t="str">
+        <f t="shared" si="2"/>
+        <v>R20260318-3-3</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>61</v>
       </c>
@@ -5634,8 +6003,12 @@
         <f t="shared" si="0"/>
         <v>LX/VM</v>
       </c>
-    </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K70" t="str">
+        <f t="shared" si="2"/>
+        <v>R20260403-1-1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>61</v>
       </c>
@@ -5664,8 +6037,12 @@
         <f t="shared" si="0"/>
         <v>LX/MN</v>
       </c>
-    </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K71" t="str">
+        <f t="shared" si="2"/>
+        <v>R20260403-1-2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>61</v>
       </c>
@@ -5694,8 +6071,12 @@
         <f t="shared" si="0"/>
         <v>MN/VM</v>
       </c>
-    </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K72" t="str">
+        <f t="shared" si="2"/>
+        <v>R20260403-1-3</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>62</v>
       </c>
@@ -5724,8 +6105,12 @@
         <f t="shared" si="0"/>
         <v>LX/MN</v>
       </c>
-    </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K73" t="str">
+        <f t="shared" si="2"/>
+        <v>R20260403-2-1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>62</v>
       </c>
@@ -5754,8 +6139,12 @@
         <f t="shared" si="0"/>
         <v>ML/MN</v>
       </c>
-    </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K74" t="str">
+        <f t="shared" si="2"/>
+        <v>R20260403-2-2</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>62</v>
       </c>
@@ -5787,8 +6176,12 @@
       <c r="J75" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K75" t="str">
+        <f t="shared" si="2"/>
+        <v>R20260403-2-3</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>65</v>
       </c>
@@ -5817,8 +6210,12 @@
         <f t="shared" si="0"/>
         <v>LX/VM</v>
       </c>
-    </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K76" t="str">
+        <f t="shared" si="2"/>
+        <v>R20260406-1-1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>65</v>
       </c>
@@ -5847,8 +6244,12 @@
         <f t="shared" si="0"/>
         <v>LX/MN</v>
       </c>
-    </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K77" t="str">
+        <f t="shared" si="2"/>
+        <v>R20260406-1-2</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>65</v>
       </c>
@@ -5877,8 +6278,12 @@
         <f t="shared" si="0"/>
         <v>MN/VM</v>
       </c>
-    </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K78" t="str">
+        <f t="shared" si="2"/>
+        <v>R20260406-1-3</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>66</v>
       </c>
@@ -5907,8 +6312,12 @@
         <f t="shared" si="0"/>
         <v>ML/VM</v>
       </c>
-    </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K79" t="str">
+        <f t="shared" si="2"/>
+        <v>R20260406-2-1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>66</v>
       </c>
@@ -5940,8 +6349,12 @@
       <c r="J80" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="K80" t="str">
+        <f t="shared" si="2"/>
+        <v>R20260406-2-2</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>66</v>
       </c>
@@ -5969,6 +6382,10 @@
       <c r="I81" t="str">
         <f t="shared" si="0"/>
         <v>LX/ML</v>
+      </c>
+      <c r="K81" t="str">
+        <f t="shared" si="2"/>
+        <v>R20260406-2-3</v>
       </c>
     </row>
   </sheetData>
@@ -6006,6 +6423,1465 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D042676D-AD31-4A56-94A6-6312DC3D8F3D}">
+  <dimension ref="A1:I86"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="15.1796875" customWidth="1"/>
+    <col min="2" max="2" width="9.90625" customWidth="1"/>
+    <col min="4" max="5" width="8.7265625" style="5"/>
+    <col min="7" max="8" width="13.54296875" customWidth="1"/>
+    <col min="9" max="9" width="9.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="F1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H1" t="s">
+        <v>85</v>
+      </c>
+      <c r="I1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F5" t="s">
+        <v>69</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>77</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F7" t="s">
+        <v>69</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>77</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>77</v>
+      </c>
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>83</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>83</v>
+      </c>
+      <c r="B11">
+        <v>2</v>
+      </c>
+      <c r="C11" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>83</v>
+      </c>
+      <c r="B12">
+        <v>3</v>
+      </c>
+      <c r="C12" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>83</v>
+      </c>
+      <c r="B13">
+        <v>4</v>
+      </c>
+      <c r="C13" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>83</v>
+      </c>
+      <c r="B14">
+        <v>5</v>
+      </c>
+      <c r="C14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>83</v>
+      </c>
+      <c r="B15">
+        <v>6</v>
+      </c>
+      <c r="C15" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>84</v>
+      </c>
+      <c r="B16">
+        <v>1</v>
+      </c>
+      <c r="C16" t="s">
+        <v>12</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>84</v>
+      </c>
+      <c r="B17">
+        <v>2</v>
+      </c>
+      <c r="C17" t="s">
+        <v>12</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>84</v>
+      </c>
+      <c r="B18">
+        <v>3</v>
+      </c>
+      <c r="C18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="F18" t="s">
+        <v>87</v>
+      </c>
+      <c r="H18" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>84</v>
+      </c>
+      <c r="B19">
+        <v>4</v>
+      </c>
+      <c r="C19" t="s">
+        <v>15</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>84</v>
+      </c>
+      <c r="B20">
+        <v>5</v>
+      </c>
+      <c r="C20" t="s">
+        <v>15</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>84</v>
+      </c>
+      <c r="B21">
+        <v>6</v>
+      </c>
+      <c r="C21" t="s">
+        <v>13</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>89</v>
+      </c>
+      <c r="B22">
+        <v>1</v>
+      </c>
+      <c r="C22" t="s">
+        <v>12</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>89</v>
+      </c>
+      <c r="B23">
+        <v>2</v>
+      </c>
+      <c r="C23" t="s">
+        <v>12</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>89</v>
+      </c>
+      <c r="B24">
+        <v>3</v>
+      </c>
+      <c r="C24" t="s">
+        <v>12</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F24" t="s">
+        <v>69</v>
+      </c>
+      <c r="G24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>89</v>
+      </c>
+      <c r="B25">
+        <v>4</v>
+      </c>
+      <c r="C25" t="s">
+        <v>15</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>89</v>
+      </c>
+      <c r="B26">
+        <v>5</v>
+      </c>
+      <c r="C26" t="s">
+        <v>15</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>89</v>
+      </c>
+      <c r="B27">
+        <v>6</v>
+      </c>
+      <c r="C27" t="s">
+        <v>15</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>89</v>
+      </c>
+      <c r="B28">
+        <v>7</v>
+      </c>
+      <c r="C28" t="s">
+        <v>14</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>89</v>
+      </c>
+      <c r="B29">
+        <v>8</v>
+      </c>
+      <c r="C29" t="s">
+        <v>14</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>89</v>
+      </c>
+      <c r="B30">
+        <v>9</v>
+      </c>
+      <c r="C30" t="s">
+        <v>14</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>89</v>
+      </c>
+      <c r="B31">
+        <v>10</v>
+      </c>
+      <c r="C31" t="s">
+        <v>13</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>90</v>
+      </c>
+      <c r="B32">
+        <v>1</v>
+      </c>
+      <c r="C32" t="s">
+        <v>14</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F32" t="s">
+        <v>69</v>
+      </c>
+      <c r="G32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>90</v>
+      </c>
+      <c r="B33">
+        <v>2</v>
+      </c>
+      <c r="C33" t="s">
+        <v>14</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>90</v>
+      </c>
+      <c r="B34">
+        <v>3</v>
+      </c>
+      <c r="C34" t="s">
+        <v>15</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="E34" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>90</v>
+      </c>
+      <c r="B35">
+        <v>4</v>
+      </c>
+      <c r="C35" t="s">
+        <v>14</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>90</v>
+      </c>
+      <c r="B36">
+        <v>5</v>
+      </c>
+      <c r="C36" t="s">
+        <v>12</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="E36" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>90</v>
+      </c>
+      <c r="B37">
+        <v>6</v>
+      </c>
+      <c r="C37" t="s">
+        <v>13</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="E37" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>91</v>
+      </c>
+      <c r="B38">
+        <v>1</v>
+      </c>
+      <c r="C38" t="s">
+        <v>14</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="E38" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>91</v>
+      </c>
+      <c r="B39">
+        <v>2</v>
+      </c>
+      <c r="C39" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="E39" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>91</v>
+      </c>
+      <c r="B40">
+        <v>3</v>
+      </c>
+      <c r="C40" t="s">
+        <v>13</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="E40" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>91</v>
+      </c>
+      <c r="B41">
+        <v>4</v>
+      </c>
+      <c r="C41" t="s">
+        <v>12</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="E41" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>91</v>
+      </c>
+      <c r="B42">
+        <v>5</v>
+      </c>
+      <c r="C42" t="s">
+        <v>15</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="E42" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>91</v>
+      </c>
+      <c r="B43">
+        <v>6</v>
+      </c>
+      <c r="C43" t="s">
+        <v>12</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="E43" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>91</v>
+      </c>
+      <c r="B44">
+        <v>7</v>
+      </c>
+      <c r="C44" t="s">
+        <v>12</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="E44" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>91</v>
+      </c>
+      <c r="B45">
+        <v>8</v>
+      </c>
+      <c r="C45" t="s">
+        <v>13</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>91</v>
+      </c>
+      <c r="B46">
+        <v>9</v>
+      </c>
+      <c r="C46" t="s">
+        <v>14</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="E46" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>91</v>
+      </c>
+      <c r="B47">
+        <v>10</v>
+      </c>
+      <c r="C47" t="s">
+        <v>13</v>
+      </c>
+      <c r="D47" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="E47" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
+        <v>92</v>
+      </c>
+      <c r="B48">
+        <v>1</v>
+      </c>
+      <c r="C48" t="s">
+        <v>14</v>
+      </c>
+      <c r="D48" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="E48" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
+        <v>92</v>
+      </c>
+      <c r="B49">
+        <v>2</v>
+      </c>
+      <c r="C49" t="s">
+        <v>14</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="E49" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>92</v>
+      </c>
+      <c r="B50">
+        <v>3</v>
+      </c>
+      <c r="C50" t="s">
+        <v>13</v>
+      </c>
+      <c r="D50" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="E50" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
+        <v>92</v>
+      </c>
+      <c r="B51">
+        <v>4</v>
+      </c>
+      <c r="C51" t="s">
+        <v>12</v>
+      </c>
+      <c r="D51" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="E51" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
+        <v>92</v>
+      </c>
+      <c r="B52">
+        <v>5</v>
+      </c>
+      <c r="C52" t="s">
+        <v>14</v>
+      </c>
+      <c r="D52" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
+        <v>92</v>
+      </c>
+      <c r="B53">
+        <v>6</v>
+      </c>
+      <c r="C53" t="s">
+        <v>15</v>
+      </c>
+      <c r="D53" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="E53" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
+        <v>92</v>
+      </c>
+      <c r="B54">
+        <v>7</v>
+      </c>
+      <c r="C54" t="s">
+        <v>13</v>
+      </c>
+      <c r="D54" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="E54" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
+        <v>92</v>
+      </c>
+      <c r="B55">
+        <v>8</v>
+      </c>
+      <c r="C55" t="s">
+        <v>13</v>
+      </c>
+      <c r="D55" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="E55" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
+        <v>92</v>
+      </c>
+      <c r="B56">
+        <v>9</v>
+      </c>
+      <c r="C56" t="s">
+        <v>15</v>
+      </c>
+      <c r="D56" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="E56" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
+        <v>93</v>
+      </c>
+      <c r="B57">
+        <v>1</v>
+      </c>
+      <c r="C57" t="s">
+        <v>14</v>
+      </c>
+      <c r="D57" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="E57" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
+        <v>93</v>
+      </c>
+      <c r="B58">
+        <v>2</v>
+      </c>
+      <c r="C58" t="s">
+        <v>13</v>
+      </c>
+      <c r="D58" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="E58" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
+        <v>93</v>
+      </c>
+      <c r="B59">
+        <v>3</v>
+      </c>
+      <c r="C59" t="s">
+        <v>15</v>
+      </c>
+      <c r="D59" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="E59" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
+        <v>93</v>
+      </c>
+      <c r="B60">
+        <v>4</v>
+      </c>
+      <c r="C60" t="s">
+        <v>12</v>
+      </c>
+      <c r="D60" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="E60" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
+        <v>93</v>
+      </c>
+      <c r="B61">
+        <v>5</v>
+      </c>
+      <c r="C61" t="s">
+        <v>13</v>
+      </c>
+      <c r="D61" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="E61" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
+        <v>93</v>
+      </c>
+      <c r="B62">
+        <v>6</v>
+      </c>
+      <c r="C62" t="s">
+        <v>15</v>
+      </c>
+      <c r="D62" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="E62" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
+        <v>93</v>
+      </c>
+      <c r="B63">
+        <v>7</v>
+      </c>
+      <c r="C63" t="s">
+        <v>13</v>
+      </c>
+      <c r="D63" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="E63" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
+        <v>93</v>
+      </c>
+      <c r="B64">
+        <v>8</v>
+      </c>
+      <c r="C64" t="s">
+        <v>14</v>
+      </c>
+      <c r="D64" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="E64" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
+        <v>93</v>
+      </c>
+      <c r="B65">
+        <v>9</v>
+      </c>
+      <c r="C65" t="s">
+        <v>14</v>
+      </c>
+      <c r="D65" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="E65" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
+        <v>94</v>
+      </c>
+      <c r="C66" t="s">
+        <v>14</v>
+      </c>
+      <c r="D66" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="E66" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F66" t="s">
+        <v>69</v>
+      </c>
+      <c r="G66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
+        <v>94</v>
+      </c>
+      <c r="C67" t="s">
+        <v>14</v>
+      </c>
+      <c r="D67" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="E67" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="F67" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A68" t="s">
+        <v>94</v>
+      </c>
+      <c r="C68" t="s">
+        <v>14</v>
+      </c>
+      <c r="D68" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="E68" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A69" t="s">
+        <v>94</v>
+      </c>
+      <c r="C69" t="s">
+        <v>14</v>
+      </c>
+      <c r="D69" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="E69" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A70" t="s">
+        <v>94</v>
+      </c>
+      <c r="C70" t="s">
+        <v>15</v>
+      </c>
+      <c r="D70" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="E70" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A71" t="s">
+        <v>94</v>
+      </c>
+      <c r="C71" t="s">
+        <v>15</v>
+      </c>
+      <c r="D71" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="E71" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A72" t="s">
+        <v>94</v>
+      </c>
+      <c r="C72" t="s">
+        <v>15</v>
+      </c>
+      <c r="D72" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="E72" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A73" t="s">
+        <v>94</v>
+      </c>
+      <c r="C73" t="s">
+        <v>15</v>
+      </c>
+      <c r="D73" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="E73" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A74" t="s">
+        <v>96</v>
+      </c>
+      <c r="C74" t="s">
+        <v>14</v>
+      </c>
+      <c r="D74" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="E74" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A75" t="s">
+        <v>96</v>
+      </c>
+      <c r="C75" t="s">
+        <v>14</v>
+      </c>
+      <c r="D75" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="E75" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A76" t="s">
+        <v>96</v>
+      </c>
+      <c r="C76" t="s">
+        <v>14</v>
+      </c>
+      <c r="D76" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="E76" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A77" t="s">
+        <v>96</v>
+      </c>
+      <c r="C77" t="s">
+        <v>15</v>
+      </c>
+      <c r="D77" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="E77" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A78" t="s">
+        <v>96</v>
+      </c>
+      <c r="C78" t="s">
+        <v>15</v>
+      </c>
+      <c r="D78" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="E78" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A79" t="s">
+        <v>96</v>
+      </c>
+      <c r="C79" t="s">
+        <v>13</v>
+      </c>
+      <c r="D79" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="E79" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A80" t="s">
+        <v>96</v>
+      </c>
+      <c r="C80" t="s">
+        <v>13</v>
+      </c>
+      <c r="D80" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="E80" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A81" t="s">
+        <v>97</v>
+      </c>
+      <c r="C81" t="s">
+        <v>14</v>
+      </c>
+      <c r="D81" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="E81" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A82" t="s">
+        <v>97</v>
+      </c>
+      <c r="C82" t="s">
+        <v>15</v>
+      </c>
+      <c r="D82" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="E82" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A83" t="s">
+        <v>97</v>
+      </c>
+      <c r="C83" t="s">
+        <v>15</v>
+      </c>
+      <c r="D83" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="E83" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A84" t="s">
+        <v>97</v>
+      </c>
+      <c r="C84" t="s">
+        <v>12</v>
+      </c>
+      <c r="D84" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="E84" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A85" t="s">
+        <v>97</v>
+      </c>
+      <c r="C85" t="s">
+        <v>13</v>
+      </c>
+      <c r="D85" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="E85" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A86" t="s">
+        <v>97</v>
+      </c>
+      <c r="C86" t="s">
+        <v>13</v>
+      </c>
+      <c r="D86" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="E86" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="F86" t="s">
+        <v>87</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32F4F995-3173-4CED-AE50-0BFB7C5A5258}">
   <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>

--- a/docs/stats.xlsx
+++ b/docs/stats.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl$\Ubuntu\home\marc\GitHub\304-game\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\marc\GitHub\304-game\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F2ED69B-B1C8-4191-A81E-6286911A3BF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26D2BED9-39A2-4A0E-B506-5E00ABAE64D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="11370" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Revolutions" sheetId="1" r:id="rId1"/>
     <sheet name="Matches" sheetId="3" r:id="rId2"/>
-    <sheet name="Betting" sheetId="5" r:id="rId3"/>
+    <sheet name="Betting" sheetId="5" state="hidden" r:id="rId3"/>
     <sheet name="By Player" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="812" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="842" uniqueCount="100">
   <si>
     <t>Date</t>
   </si>
@@ -359,6 +359,12 @@
   </si>
   <si>
     <t>R20260303-3-3</t>
+  </si>
+  <si>
+    <t>R20260427-1</t>
+  </si>
+  <si>
+    <t>R20260427-2</t>
   </si>
 </sst>
 </file>
@@ -788,7 +794,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J28"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18.90625" customWidth="1"/>
@@ -949,7 +955,7 @@
         <v>0.85416666666666663</v>
       </c>
       <c r="E3" s="3">
-        <f t="shared" ref="E3:E28" si="1">MOD(D3 - C3, 1)</f>
+        <f t="shared" ref="E3:E30" si="1">MOD(D3 - C3, 1)</f>
         <v>0.16666666666666663</v>
       </c>
       <c r="F3" t="str" cm="1">
@@ -3476,8 +3482,200 @@
         <v>2 (29)</v>
       </c>
     </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A29" t="str">
+        <f t="shared" ref="A29:A34" si="3">"R"&amp;TEXT(B29,"yyyymmdd")&amp;"-"&amp;COUNTIFS($B:$B,B29,$C:$C,"&lt;="&amp;C29)</f>
+        <v>R20260427-1</v>
+      </c>
+      <c r="B29" s="1">
+        <v>46139</v>
+      </c>
+      <c r="C29" s="2">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F29" t="str" cm="1">
+        <f t="array" ref="F29">COUNTIFS(
+ Matches!$A$2:$A$200,$A29,
+ Matches!$I$2:$I$200,"*"&amp;F$1&amp;"*"
+)
+&amp;" ("&amp;
+SUMPRODUCT(
+ (Matches!$A$2:$A$200=$A29) *
+ ((Matches!$C$2:$C$200=F$1)+(Matches!$D$2:$D$200=F$1)) *
+ Matches!$G$2:$G$200
+)
++
+SUMPRODUCT(
+ (Matches!$A$2:$A$200=$A29) *
+ ((Matches!$E$2:$E$200=F$1)+(Matches!$F$2:$F$200=F$1)) *
+ Matches!$H$2:$H$200
+)
+&amp;")"</f>
+        <v>2 (24)</v>
+      </c>
+      <c r="G29" t="str" cm="1">
+        <f t="array" ref="G29">COUNTIFS(
+ Matches!$A$2:$A$200,$A29,
+ Matches!$I$2:$I$200,"*"&amp;G$1&amp;"*"
+)
+&amp;" ("&amp;
+SUMPRODUCT(
+ (Matches!$A$2:$A$200=$A29) *
+ ((Matches!$C$2:$C$200=G$1)+(Matches!$D$2:$D$200=G$1)) *
+ Matches!$G$2:$G$200
+)
++
+SUMPRODUCT(
+ (Matches!$A$2:$A$200=$A29) *
+ ((Matches!$E$2:$E$200=G$1)+(Matches!$F$2:$F$200=G$1)) *
+ Matches!$H$2:$H$200
+)
+&amp;")"</f>
+        <v>2 (29)</v>
+      </c>
+      <c r="H29" t="str" cm="1">
+        <f t="array" ref="H29">COUNTIFS(
+ Matches!$A$2:$A$200,$A29,
+ Matches!$I$2:$I$200,"*"&amp;H$1&amp;"*"
+)
+&amp;" ("&amp;
+SUMPRODUCT(
+ (Matches!$A$2:$A$200=$A29) *
+ ((Matches!$C$2:$C$200=H$1)+(Matches!$D$2:$D$200=H$1)) *
+ Matches!$G$2:$G$200
+)
++
+SUMPRODUCT(
+ (Matches!$A$2:$A$200=$A29) *
+ ((Matches!$E$2:$E$200=H$1)+(Matches!$F$2:$F$200=H$1)) *
+ Matches!$H$2:$H$200
+)
+&amp;")"</f>
+        <v>2 (25)</v>
+      </c>
+      <c r="I29" t="str" cm="1">
+        <f t="array" ref="I29">COUNTIFS(
+ Matches!$A$2:$A$200,$A29,
+ Matches!$I$2:$I$200,"*"&amp;I$1&amp;"*"
+)
+&amp;" ("&amp;
+SUMPRODUCT(
+ (Matches!$A$2:$A$200=$A29) *
+ ((Matches!$C$2:$C$200=I$1)+(Matches!$D$2:$D$200=I$1)) *
+ Matches!$G$2:$G$200
+)
++
+SUMPRODUCT(
+ (Matches!$A$2:$A$200=$A29) *
+ ((Matches!$E$2:$E$200=I$1)+(Matches!$F$2:$F$200=I$1)) *
+ Matches!$H$2:$H$200
+)
+&amp;")"</f>
+        <v>0 (18)</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A30" t="str">
+        <f t="shared" si="3"/>
+        <v>R20260427-2</v>
+      </c>
+      <c r="B30" s="1">
+        <v>46139</v>
+      </c>
+      <c r="C30" s="2">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="E30" s="3">
+        <f t="shared" si="1"/>
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="F30" t="str" cm="1">
+        <f t="array" ref="F30">COUNTIFS(
+ Matches!$A$2:$A$200,$A30,
+ Matches!$I$2:$I$200,"*"&amp;F$1&amp;"*"
+)
+&amp;" ("&amp;
+SUMPRODUCT(
+ (Matches!$A$2:$A$200=$A30) *
+ ((Matches!$C$2:$C$200=F$1)+(Matches!$D$2:$D$200=F$1)) *
+ Matches!$G$2:$G$200
+)
++
+SUMPRODUCT(
+ (Matches!$A$2:$A$200=$A30) *
+ ((Matches!$E$2:$E$200=F$1)+(Matches!$F$2:$F$200=F$1)) *
+ Matches!$H$2:$H$200
+)
+&amp;")"</f>
+        <v>1 (18)</v>
+      </c>
+      <c r="G30" t="str" cm="1">
+        <f t="array" ref="G30">COUNTIFS(
+ Matches!$A$2:$A$200,$A30,
+ Matches!$I$2:$I$200,"*"&amp;G$1&amp;"*"
+)
+&amp;" ("&amp;
+SUMPRODUCT(
+ (Matches!$A$2:$A$200=$A30) *
+ ((Matches!$C$2:$C$200=G$1)+(Matches!$D$2:$D$200=G$1)) *
+ Matches!$G$2:$G$200
+)
++
+SUMPRODUCT(
+ (Matches!$A$2:$A$200=$A30) *
+ ((Matches!$E$2:$E$200=G$1)+(Matches!$F$2:$F$200=G$1)) *
+ Matches!$H$2:$H$200
+)
+&amp;")"</f>
+        <v>3 (30)</v>
+      </c>
+      <c r="H30" t="str" cm="1">
+        <f t="array" ref="H30">COUNTIFS(
+ Matches!$A$2:$A$200,$A30,
+ Matches!$I$2:$I$200,"*"&amp;H$1&amp;"*"
+)
+&amp;" ("&amp;
+SUMPRODUCT(
+ (Matches!$A$2:$A$200=$A30) *
+ ((Matches!$C$2:$C$200=H$1)+(Matches!$D$2:$D$200=H$1)) *
+ Matches!$G$2:$G$200
+)
++
+SUMPRODUCT(
+ (Matches!$A$2:$A$200=$A30) *
+ ((Matches!$E$2:$E$200=H$1)+(Matches!$F$2:$F$200=H$1)) *
+ Matches!$H$2:$H$200
+)
+&amp;")"</f>
+        <v>1 (19)</v>
+      </c>
+      <c r="I30" t="str" cm="1">
+        <f t="array" ref="I30">COUNTIFS(
+ Matches!$A$2:$A$200,$A30,
+ Matches!$I$2:$I$200,"*"&amp;I$1&amp;"*"
+)
+&amp;" ("&amp;
+SUMPRODUCT(
+ (Matches!$A$2:$A$200=$A30) *
+ ((Matches!$C$2:$C$200=I$1)+(Matches!$D$2:$D$200=I$1)) *
+ Matches!$G$2:$G$200
+)
++
+SUMPRODUCT(
+ (Matches!$A$2:$A$200=$A30) *
+ ((Matches!$E$2:$E$200=I$1)+(Matches!$F$2:$F$200=I$1)) *
+ Matches!$H$2:$H$200
+)
+&amp;")"</f>
+        <v>1 (13)</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="F2:I29">
+  <conditionalFormatting sqref="F2:I30">
     <cfRule type="expression" dxfId="10" priority="1">
       <formula>LEFT(F2,1)="0"</formula>
     </cfRule>
@@ -3508,7 +3706,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B6F95CC-DDBC-4D0D-92B0-0E6D3AF66C09}">
-  <dimension ref="A1:K81"/>
+  <dimension ref="A1:K87"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.90625" customWidth="1"/>
@@ -3622,7 +3820,7 @@
         <v>10</v>
       </c>
       <c r="I3" t="str">
-        <f t="shared" ref="I3:I81" si="0">IF(G3&gt;H3,
+        <f t="shared" ref="I3:I87" si="0">IF(G3&gt;H3,
    IF(C3&lt;D3, C3&amp;"/"&amp;D3, D3&amp;"/"&amp;C3),
    IF(E3&lt;F3, E3&amp;"/"&amp;F3, F3&amp;"/"&amp;E3)
 )</f>
@@ -5896,7 +6094,7 @@
         <v>ML/MN</v>
       </c>
       <c r="K67" t="str">
-        <f t="shared" ref="K67:K81" si="2">_xlfn.CONCAT(A67, "-", B67)</f>
+        <f t="shared" ref="K67:K87" si="2">_xlfn.CONCAT(A67, "-", B67)</f>
         <v>R20260318-3-1</v>
       </c>
     </row>
@@ -6386,6 +6584,210 @@
       <c r="K81" t="str">
         <f t="shared" si="2"/>
         <v>R20260406-2-3</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A82" t="s">
+        <v>98</v>
+      </c>
+      <c r="B82">
+        <v>1</v>
+      </c>
+      <c r="C82" t="s">
+        <v>13</v>
+      </c>
+      <c r="D82" t="s">
+        <v>15</v>
+      </c>
+      <c r="E82" t="s">
+        <v>14</v>
+      </c>
+      <c r="F82" t="s">
+        <v>12</v>
+      </c>
+      <c r="G82" s="4">
+        <v>9</v>
+      </c>
+      <c r="H82" s="4">
+        <v>10</v>
+      </c>
+      <c r="I82" t="str">
+        <f t="shared" si="0"/>
+        <v>LX/MN</v>
+      </c>
+      <c r="K82" t="str">
+        <f t="shared" si="2"/>
+        <v>R20260427-1-1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A83" t="s">
+        <v>98</v>
+      </c>
+      <c r="B83">
+        <v>2</v>
+      </c>
+      <c r="C83" t="s">
+        <v>14</v>
+      </c>
+      <c r="D83" t="s">
+        <v>13</v>
+      </c>
+      <c r="E83" t="s">
+        <v>12</v>
+      </c>
+      <c r="F83" t="s">
+        <v>15</v>
+      </c>
+      <c r="G83" s="4">
+        <v>5</v>
+      </c>
+      <c r="H83" s="4">
+        <v>10</v>
+      </c>
+      <c r="I83" t="str">
+        <f t="shared" si="0"/>
+        <v>LX/ML</v>
+      </c>
+      <c r="K83" t="str">
+        <f t="shared" si="2"/>
+        <v>R20260427-1-2</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A84" t="s">
+        <v>98</v>
+      </c>
+      <c r="B84">
+        <v>3</v>
+      </c>
+      <c r="C84" t="s">
+        <v>13</v>
+      </c>
+      <c r="D84" t="s">
+        <v>12</v>
+      </c>
+      <c r="E84" t="s">
+        <v>14</v>
+      </c>
+      <c r="F84" t="s">
+        <v>15</v>
+      </c>
+      <c r="G84" s="4">
+        <v>4</v>
+      </c>
+      <c r="H84" s="4">
+        <v>10</v>
+      </c>
+      <c r="I84" t="str">
+        <f t="shared" si="0"/>
+        <v>ML/MN</v>
+      </c>
+      <c r="K84" t="str">
+        <f t="shared" si="2"/>
+        <v>R20260427-1-3</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A85" t="s">
+        <v>99</v>
+      </c>
+      <c r="B85">
+        <v>1</v>
+      </c>
+      <c r="C85" t="s">
+        <v>13</v>
+      </c>
+      <c r="D85" t="s">
+        <v>12</v>
+      </c>
+      <c r="E85" t="s">
+        <v>14</v>
+      </c>
+      <c r="F85" t="s">
+        <v>15</v>
+      </c>
+      <c r="G85" s="4">
+        <v>1</v>
+      </c>
+      <c r="H85" s="4">
+        <v>10</v>
+      </c>
+      <c r="I85" t="str">
+        <f t="shared" si="0"/>
+        <v>ML/MN</v>
+      </c>
+      <c r="K85" t="str">
+        <f t="shared" si="2"/>
+        <v>R20260427-2-1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A86" t="s">
+        <v>99</v>
+      </c>
+      <c r="B86">
+        <v>2</v>
+      </c>
+      <c r="C86" t="s">
+        <v>14</v>
+      </c>
+      <c r="D86" t="s">
+        <v>12</v>
+      </c>
+      <c r="E86" t="s">
+        <v>15</v>
+      </c>
+      <c r="F86" t="s">
+        <v>13</v>
+      </c>
+      <c r="G86" s="4">
+        <v>7</v>
+      </c>
+      <c r="H86" s="4">
+        <v>10</v>
+      </c>
+      <c r="I86" t="str">
+        <f t="shared" si="0"/>
+        <v>ML/VM</v>
+      </c>
+      <c r="K86" t="str">
+        <f t="shared" si="2"/>
+        <v>R20260427-2-2</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A87" t="s">
+        <v>99</v>
+      </c>
+      <c r="B87">
+        <v>3</v>
+      </c>
+      <c r="C87" t="s">
+        <v>13</v>
+      </c>
+      <c r="D87" t="s">
+        <v>14</v>
+      </c>
+      <c r="E87" t="s">
+        <v>15</v>
+      </c>
+      <c r="F87" t="s">
+        <v>12</v>
+      </c>
+      <c r="G87" s="4">
+        <v>2</v>
+      </c>
+      <c r="H87" s="4">
+        <v>10</v>
+      </c>
+      <c r="I87" t="str">
+        <f t="shared" si="0"/>
+        <v>LX/ML</v>
+      </c>
+      <c r="K87" t="str">
+        <f t="shared" si="2"/>
+        <v>R20260427-2-3</v>
       </c>
     </row>
   </sheetData>
@@ -6414,7 +6816,7 @@
           <x14:formula1>
             <xm:f>Revolutions!$A:$A</xm:f>
           </x14:formula1>
-          <xm:sqref>A1:A69 A82:A1048576</xm:sqref>
+          <xm:sqref>A1:A69 A88:A1048576</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -7948,11 +8350,11 @@
       </c>
       <c r="D2" cm="1">
         <f t="array" aca="1" ref="D2" ca="1">SUMPRODUCT(--LEFT(INDIRECT("Revolutions!F2:F"&amp;$G$2)))</f>
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E2" cm="1">
         <f t="array" aca="1" ref="E2" ca="1">SUMPRODUCT(--MID(INDIRECT("Revolutions!F2:F"&amp;$G$2), FIND("(",INDIRECT("Revolutions!F2:F"&amp;$G$2))+1, LEN(INDIRECT("Revolutions!F2:F"&amp;$G$2))-FIND("(",INDIRECT("Revolutions!F2:F"&amp;$G$2))-1))</f>
-        <v>601</v>
+        <v>643</v>
       </c>
       <c r="F2" cm="1">
         <f t="array" aca="1" ref="F2" ca="1">SUM(
@@ -7968,11 +8370,11 @@
   )
  )
 )</f>
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="G2" cm="1">
         <f t="array" ref="G2">MATCH(2,1/(Revolutions!A:A&lt;&gt;""),1)</f>
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
@@ -8002,15 +8404,15 @@
   )
  )
 )</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D3" cm="1">
         <f t="array" aca="1" ref="D3" ca="1">SUMPRODUCT(--LEFT(INDIRECT("Revolutions!G2:G"&amp;$G$2),1))</f>
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E3" cm="1">
         <f t="array" aca="1" ref="E3" ca="1">SUMPRODUCT(--MID(INDIRECT("Revolutions!G2:G"&amp;$G$2), FIND("(",INDIRECT("Revolutions!G2:G"&amp;$G$2))+1, LEN(INDIRECT("Revolutions!G2:G"&amp;$G$2))-FIND("(",INDIRECT("Revolutions!G2:G"&amp;$G$2))-1))</f>
-        <v>595</v>
+        <v>654</v>
       </c>
       <c r="F3" cm="1">
         <f t="array" aca="1" ref="F3" ca="1">SUM(
@@ -8026,7 +8428,7 @@
   )
  )
 )</f>
-        <v>66</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
@@ -8060,11 +8462,11 @@
       </c>
       <c r="D4" cm="1">
         <f t="array" aca="1" ref="D4" ca="1">SUMPRODUCT(--LEFT(INDIRECT("Revolutions!H2:H"&amp;$G$2)))</f>
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E4" cm="1">
         <f t="array" aca="1" ref="E4" ca="1">SUMPRODUCT(--MID(INDIRECT("Revolutions!H2:H"&amp;$G$2), FIND("(",INDIRECT("Revolutions!H2:H"&amp;$G$2))+1, LEN(INDIRECT("Revolutions!H2:H"&amp;$G$2))-FIND("(",INDIRECT("Revolutions!H2:H"&amp;$G$2))-1))</f>
-        <v>640</v>
+        <v>684</v>
       </c>
       <c r="F4" cm="1">
         <f t="array" aca="1" ref="F4" ca="1">SUM(
@@ -8080,7 +8482,7 @@
   )
  )
 )</f>
-        <v>77</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
@@ -8114,11 +8516,11 @@
       </c>
       <c r="D5" cm="1">
         <f t="array" aca="1" ref="D5" ca="1">SUMPRODUCT(--LEFT(INDIRECT("Revolutions!I2:I"&amp;$G$2),1))</f>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E5" cm="1">
         <f t="array" aca="1" ref="E5" ca="1">SUMPRODUCT(--MID(INDIRECT("Revolutions!I2:I"&amp;$G$2), FIND("(",INDIRECT("Revolutions!I2:I"&amp;$G$2))+1, LEN(INDIRECT("Revolutions!I2:I"&amp;$G$2))-FIND("(",INDIRECT("Revolutions!I2:I"&amp;$G$2))-1))</f>
-        <v>588</v>
+        <v>619</v>
       </c>
       <c r="F5" cm="1">
         <f t="array" aca="1" ref="F5" ca="1">SUM(
@@ -8134,7 +8536,7 @@
   )
  )
 )</f>
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>

--- a/docs/stats.xlsx
+++ b/docs/stats.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\marc\GitHub\304-game\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26D2BED9-39A2-4A0E-B506-5E00ABAE64D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{284A3E24-A130-43C3-A19A-AEC7EFEDE3E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Revolutions" sheetId="1" r:id="rId1"/>
@@ -509,6 +509,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3484,7 +3488,7 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A29" t="str">
-        <f t="shared" ref="A29:A34" si="3">"R"&amp;TEXT(B29,"yyyymmdd")&amp;"-"&amp;COUNTIFS($B:$B,B29,$C:$C,"&lt;="&amp;C29)</f>
+        <f t="shared" ref="A29:A30" si="3">"R"&amp;TEXT(B29,"yyyymmdd")&amp;"-"&amp;COUNTIFS($B:$B,B29,$C:$C,"&lt;="&amp;C29)</f>
         <v>R20260427-1</v>
       </c>
       <c r="B29" s="1">
@@ -8556,7 +8560,7 @@
     <cfRule type="top10" dxfId="1" priority="1" bottom="1" rank="1"/>
     <cfRule type="top10" dxfId="0" priority="2" rank="1"/>
   </conditionalFormatting>
-  <dataValidations xWindow="1530" yWindow="611" count="4">
+  <dataValidations xWindow="1523" yWindow="523" count="4">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="&quot;Revolutions won&quot; is the total number of revolutions won by a player. This is calculated by the winner of the most matches, tiebroken by number of stone given. If there is still a tie, both players will get a point for that given revolution." sqref="C1" xr:uid="{D3D77359-A6B3-4EEE-BEE6-F183B72A36DB}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="&quot;Matches won&quot; simply is the total number of matches won by a player. " sqref="D1" xr:uid="{5714768D-E12A-4EEB-A7A3-FDC2ADF0CE2F}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="&quot;Total stone given&quot; simply is the total number of stone given by a given player. Can be calculated from the summation of the revolution table (score in brackets)._x000a_" sqref="E1" xr:uid="{C37DAB73-96C6-4A09-AC35-E4D0BBB8EEE5}"/>

--- a/docs/stats.xlsx
+++ b/docs/stats.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\marc\GitHub\304-game\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{284A3E24-A130-43C3-A19A-AEC7EFEDE3E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B9A7D97-2F05-469D-BAFA-CF40FB7BDA55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Revolutions" sheetId="1" r:id="rId1"/>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="842" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="857" uniqueCount="101">
   <si>
     <t>Date</t>
   </si>
@@ -365,6 +365,9 @@
   </si>
   <si>
     <t>R20260427-2</t>
+  </si>
+  <si>
+    <t>R20260529-1</t>
   </si>
 </sst>
 </file>
@@ -509,10 +512,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -798,7 +797,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18.90625" customWidth="1"/>
@@ -959,7 +958,7 @@
         <v>0.85416666666666663</v>
       </c>
       <c r="E3" s="3">
-        <f t="shared" ref="E3:E30" si="1">MOD(D3 - C3, 1)</f>
+        <f t="shared" ref="E3:E31" si="1">MOD(D3 - C3, 1)</f>
         <v>0.16666666666666663</v>
       </c>
       <c r="F3" t="str" cm="1">
@@ -3488,7 +3487,7 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A29" t="str">
-        <f t="shared" ref="A29:A30" si="3">"R"&amp;TEXT(B29,"yyyymmdd")&amp;"-"&amp;COUNTIFS($B:$B,B29,$C:$C,"&lt;="&amp;C29)</f>
+        <f t="shared" ref="A29:A31" si="3">"R"&amp;TEXT(B29,"yyyymmdd")&amp;"-"&amp;COUNTIFS($B:$B,B29,$C:$C,"&lt;="&amp;C29)</f>
         <v>R20260427-1</v>
       </c>
       <c r="B29" s="1">
@@ -3678,8 +3677,104 @@
         <v>1 (13)</v>
       </c>
     </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A31" t="str">
+        <f t="shared" si="3"/>
+        <v>R20260529-1</v>
+      </c>
+      <c r="B31" s="1">
+        <v>46171</v>
+      </c>
+      <c r="C31" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E31" s="3">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="F31" t="str" cm="1">
+        <f t="array" ref="F31">COUNTIFS(
+ Matches!$A$2:$A$200,$A31,
+ Matches!$I$2:$I$200,"*"&amp;F$1&amp;"*"
+)
+&amp;" ("&amp;
+SUMPRODUCT(
+ (Matches!$A$2:$A$200=$A31) *
+ ((Matches!$C$2:$C$200=F$1)+(Matches!$D$2:$D$200=F$1)) *
+ Matches!$G$2:$G$200
+)
++
+SUMPRODUCT(
+ (Matches!$A$2:$A$200=$A31) *
+ ((Matches!$E$2:$E$200=F$1)+(Matches!$F$2:$F$200=F$1)) *
+ Matches!$H$2:$H$200
+)
+&amp;")"</f>
+        <v>2 (26)</v>
+      </c>
+      <c r="G31" t="str" cm="1">
+        <f t="array" ref="G31">COUNTIFS(
+ Matches!$A$2:$A$200,$A31,
+ Matches!$I$2:$I$200,"*"&amp;G$1&amp;"*"
+)
+&amp;" ("&amp;
+SUMPRODUCT(
+ (Matches!$A$2:$A$200=$A31) *
+ ((Matches!$C$2:$C$200=G$1)+(Matches!$D$2:$D$200=G$1)) *
+ Matches!$G$2:$G$200
+)
++
+SUMPRODUCT(
+ (Matches!$A$2:$A$200=$A31) *
+ ((Matches!$E$2:$E$200=G$1)+(Matches!$F$2:$F$200=G$1)) *
+ Matches!$H$2:$H$200
+)
+&amp;")"</f>
+        <v>2 (27)</v>
+      </c>
+      <c r="H31" t="str" cm="1">
+        <f t="array" ref="H31">COUNTIFS(
+ Matches!$A$2:$A$200,$A31,
+ Matches!$I$2:$I$200,"*"&amp;H$1&amp;"*"
+)
+&amp;" ("&amp;
+SUMPRODUCT(
+ (Matches!$A$2:$A$200=$A31) *
+ ((Matches!$C$2:$C$200=H$1)+(Matches!$D$2:$D$200=H$1)) *
+ Matches!$G$2:$G$200
+)
++
+SUMPRODUCT(
+ (Matches!$A$2:$A$200=$A31) *
+ ((Matches!$E$2:$E$200=H$1)+(Matches!$F$2:$F$200=H$1)) *
+ Matches!$H$2:$H$200
+)
+&amp;")"</f>
+        <v>2 (27)</v>
+      </c>
+      <c r="I31" t="str" cm="1">
+        <f t="array" ref="I31">COUNTIFS(
+ Matches!$A$2:$A$200,$A31,
+ Matches!$I$2:$I$200,"*"&amp;I$1&amp;"*"
+)
+&amp;" ("&amp;
+SUMPRODUCT(
+ (Matches!$A$2:$A$200=$A31) *
+ ((Matches!$C$2:$C$200=I$1)+(Matches!$D$2:$D$200=I$1)) *
+ Matches!$G$2:$G$200
+)
++
+SUMPRODUCT(
+ (Matches!$A$2:$A$200=$A31) *
+ ((Matches!$E$2:$E$200=I$1)+(Matches!$F$2:$F$200=I$1)) *
+ Matches!$H$2:$H$200
+)
+&amp;")"</f>
+        <v>0 (20)</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="F2:I30">
+  <conditionalFormatting sqref="F2:I31">
     <cfRule type="expression" dxfId="10" priority="1">
       <formula>LEFT(F2,1)="0"</formula>
     </cfRule>
@@ -3710,7 +3805,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B6F95CC-DDBC-4D0D-92B0-0E6D3AF66C09}">
-  <dimension ref="A1:K87"/>
+  <dimension ref="A1:K90"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.90625" customWidth="1"/>
@@ -3824,7 +3919,7 @@
         <v>10</v>
       </c>
       <c r="I3" t="str">
-        <f t="shared" ref="I3:I87" si="0">IF(G3&gt;H3,
+        <f t="shared" ref="I3:I90" si="0">IF(G3&gt;H3,
    IF(C3&lt;D3, C3&amp;"/"&amp;D3, D3&amp;"/"&amp;C3),
    IF(E3&lt;F3, E3&amp;"/"&amp;F3, F3&amp;"/"&amp;E3)
 )</f>
@@ -6098,7 +6193,7 @@
         <v>ML/MN</v>
       </c>
       <c r="K67" t="str">
-        <f t="shared" ref="K67:K87" si="2">_xlfn.CONCAT(A67, "-", B67)</f>
+        <f t="shared" ref="K67:K90" si="2">_xlfn.CONCAT(A67, "-", B67)</f>
         <v>R20260318-3-1</v>
       </c>
     </row>
@@ -6792,6 +6887,108 @@
       <c r="K87" t="str">
         <f t="shared" si="2"/>
         <v>R20260427-2-3</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A88" t="s">
+        <v>100</v>
+      </c>
+      <c r="B88">
+        <v>1</v>
+      </c>
+      <c r="C88" t="s">
+        <v>13</v>
+      </c>
+      <c r="D88" t="s">
+        <v>15</v>
+      </c>
+      <c r="E88" t="s">
+        <v>14</v>
+      </c>
+      <c r="F88" t="s">
+        <v>12</v>
+      </c>
+      <c r="G88" s="4">
+        <v>7</v>
+      </c>
+      <c r="H88" s="4">
+        <v>10</v>
+      </c>
+      <c r="I88" t="str">
+        <f t="shared" si="0"/>
+        <v>LX/MN</v>
+      </c>
+      <c r="K88" t="str">
+        <f t="shared" si="2"/>
+        <v>R20260529-1-1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A89" t="s">
+        <v>100</v>
+      </c>
+      <c r="B89">
+        <v>2</v>
+      </c>
+      <c r="C89" t="s">
+        <v>14</v>
+      </c>
+      <c r="D89" t="s">
+        <v>13</v>
+      </c>
+      <c r="E89" t="s">
+        <v>15</v>
+      </c>
+      <c r="F89" t="s">
+        <v>12</v>
+      </c>
+      <c r="G89" s="4">
+        <v>7</v>
+      </c>
+      <c r="H89" s="4">
+        <v>10</v>
+      </c>
+      <c r="I89" t="str">
+        <f t="shared" si="0"/>
+        <v>LX/ML</v>
+      </c>
+      <c r="K89" t="str">
+        <f t="shared" si="2"/>
+        <v>R20260529-1-2</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A90" t="s">
+        <v>100</v>
+      </c>
+      <c r="B90">
+        <v>3</v>
+      </c>
+      <c r="C90" t="s">
+        <v>12</v>
+      </c>
+      <c r="D90" t="s">
+        <v>13</v>
+      </c>
+      <c r="E90" t="s">
+        <v>15</v>
+      </c>
+      <c r="F90" t="s">
+        <v>14</v>
+      </c>
+      <c r="G90" s="4">
+        <v>6</v>
+      </c>
+      <c r="H90" s="4">
+        <v>10</v>
+      </c>
+      <c r="I90" t="str">
+        <f t="shared" si="0"/>
+        <v>ML/MN</v>
+      </c>
+      <c r="K90" t="str">
+        <f t="shared" si="2"/>
+        <v>R20260529-1-3</v>
       </c>
     </row>
   </sheetData>
@@ -6820,7 +7017,7 @@
           <x14:formula1>
             <xm:f>Revolutions!$A:$A</xm:f>
           </x14:formula1>
-          <xm:sqref>A1:A69 A88:A1048576</xm:sqref>
+          <xm:sqref>A1:A69 A91:A1048576</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -8354,11 +8551,11 @@
       </c>
       <c r="D2" cm="1">
         <f t="array" aca="1" ref="D2" ca="1">SUMPRODUCT(--LEFT(INDIRECT("Revolutions!F2:F"&amp;$G$2)))</f>
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E2" cm="1">
         <f t="array" aca="1" ref="E2" ca="1">SUMPRODUCT(--MID(INDIRECT("Revolutions!F2:F"&amp;$G$2), FIND("(",INDIRECT("Revolutions!F2:F"&amp;$G$2))+1, LEN(INDIRECT("Revolutions!F2:F"&amp;$G$2))-FIND("(",INDIRECT("Revolutions!F2:F"&amp;$G$2))-1))</f>
-        <v>643</v>
+        <v>669</v>
       </c>
       <c r="F2" cm="1">
         <f t="array" aca="1" ref="F2" ca="1">SUM(
@@ -8374,11 +8571,11 @@
   )
  )
 )</f>
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G2" cm="1">
         <f t="array" ref="G2">MATCH(2,1/(Revolutions!A:A&lt;&gt;""),1)</f>
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
@@ -8408,15 +8605,15 @@
   )
  )
 )</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" cm="1">
         <f t="array" aca="1" ref="D3" ca="1">SUMPRODUCT(--LEFT(INDIRECT("Revolutions!G2:G"&amp;$G$2),1))</f>
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E3" cm="1">
         <f t="array" aca="1" ref="E3" ca="1">SUMPRODUCT(--MID(INDIRECT("Revolutions!G2:G"&amp;$G$2), FIND("(",INDIRECT("Revolutions!G2:G"&amp;$G$2))+1, LEN(INDIRECT("Revolutions!G2:G"&amp;$G$2))-FIND("(",INDIRECT("Revolutions!G2:G"&amp;$G$2))-1))</f>
-        <v>654</v>
+        <v>681</v>
       </c>
       <c r="F3" cm="1">
         <f t="array" aca="1" ref="F3" ca="1">SUM(
@@ -8432,7 +8629,7 @@
   )
  )
 )</f>
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
@@ -8462,15 +8659,15 @@
   )
  )
 )</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D4" cm="1">
         <f t="array" aca="1" ref="D4" ca="1">SUMPRODUCT(--LEFT(INDIRECT("Revolutions!H2:H"&amp;$G$2)))</f>
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E4" cm="1">
         <f t="array" aca="1" ref="E4" ca="1">SUMPRODUCT(--MID(INDIRECT("Revolutions!H2:H"&amp;$G$2), FIND("(",INDIRECT("Revolutions!H2:H"&amp;$G$2))+1, LEN(INDIRECT("Revolutions!H2:H"&amp;$G$2))-FIND("(",INDIRECT("Revolutions!H2:H"&amp;$G$2))-1))</f>
-        <v>684</v>
+        <v>711</v>
       </c>
       <c r="F4" cm="1">
         <f t="array" aca="1" ref="F4" ca="1">SUM(
@@ -8486,7 +8683,7 @@
   )
  )
 )</f>
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
@@ -8524,7 +8721,7 @@
       </c>
       <c r="E5" cm="1">
         <f t="array" aca="1" ref="E5" ca="1">SUMPRODUCT(--MID(INDIRECT("Revolutions!I2:I"&amp;$G$2), FIND("(",INDIRECT("Revolutions!I2:I"&amp;$G$2))+1, LEN(INDIRECT("Revolutions!I2:I"&amp;$G$2))-FIND("(",INDIRECT("Revolutions!I2:I"&amp;$G$2))-1))</f>
-        <v>619</v>
+        <v>639</v>
       </c>
       <c r="F5" cm="1">
         <f t="array" aca="1" ref="F5" ca="1">SUM(
@@ -8540,7 +8737,7 @@
   )
  )
 )</f>
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>

--- a/docs/stats.xlsx
+++ b/docs/stats.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\marc\GitHub\304-game\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B9A7D97-2F05-469D-BAFA-CF40FB7BDA55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{226B2D8F-8E9C-4084-98E0-13FC6F7DBC2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="857" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="873" uniqueCount="103">
   <si>
     <t>Date</t>
   </si>
@@ -368,6 +368,12 @@
   </si>
   <si>
     <t>R20260529-1</t>
+  </si>
+  <si>
+    <t>SEASON 2 START</t>
+  </si>
+  <si>
+    <t>R20260725-1</t>
   </si>
 </sst>
 </file>
@@ -797,7 +803,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:J32"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18.90625" customWidth="1"/>
@@ -958,7 +964,7 @@
         <v>0.85416666666666663</v>
       </c>
       <c r="E3" s="3">
-        <f t="shared" ref="E3:E31" si="1">MOD(D3 - C3, 1)</f>
+        <f t="shared" ref="E3:E32" si="1">MOD(D3 - C3, 1)</f>
         <v>0.16666666666666663</v>
       </c>
       <c r="F3" t="str" cm="1">
@@ -3487,7 +3493,7 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A29" t="str">
-        <f t="shared" ref="A29:A31" si="3">"R"&amp;TEXT(B29,"yyyymmdd")&amp;"-"&amp;COUNTIFS($B:$B,B29,$C:$C,"&lt;="&amp;C29)</f>
+        <f t="shared" ref="A29:A32" si="3">"R"&amp;TEXT(B29,"yyyymmdd")&amp;"-"&amp;COUNTIFS($B:$B,B29,$C:$C,"&lt;="&amp;C29)</f>
         <v>R20260427-1</v>
       </c>
       <c r="B29" s="1">
@@ -3773,8 +3779,107 @@
         <v>0 (20)</v>
       </c>
     </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A32" t="str">
+        <f t="shared" si="3"/>
+        <v>R20260725-1</v>
+      </c>
+      <c r="B32" s="1">
+        <v>46228</v>
+      </c>
+      <c r="C32" s="2">
+        <v>12</v>
+      </c>
+      <c r="E32" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F32" t="str" cm="1">
+        <f t="array" ref="F32">COUNTIFS(
+ Matches!$A$2:$A$200,$A32,
+ Matches!$I$2:$I$200,"*"&amp;F$1&amp;"*"
+)
+&amp;" ("&amp;
+SUMPRODUCT(
+ (Matches!$A$2:$A$200=$A32) *
+ ((Matches!$C$2:$C$200=F$1)+(Matches!$D$2:$D$200=F$1)) *
+ Matches!$G$2:$G$200
+)
++
+SUMPRODUCT(
+ (Matches!$A$2:$A$200=$A32) *
+ ((Matches!$E$2:$E$200=F$1)+(Matches!$F$2:$F$200=F$1)) *
+ Matches!$H$2:$H$200
+)
+&amp;")"</f>
+        <v>2 (27)</v>
+      </c>
+      <c r="G32" t="str" cm="1">
+        <f t="array" ref="G32">COUNTIFS(
+ Matches!$A$2:$A$200,$A32,
+ Matches!$I$2:$I$200,"*"&amp;G$1&amp;"*"
+)
+&amp;" ("&amp;
+SUMPRODUCT(
+ (Matches!$A$2:$A$200=$A32) *
+ ((Matches!$C$2:$C$200=G$1)+(Matches!$D$2:$D$200=G$1)) *
+ Matches!$G$2:$G$200
+)
++
+SUMPRODUCT(
+ (Matches!$A$2:$A$200=$A32) *
+ ((Matches!$E$2:$E$200=G$1)+(Matches!$F$2:$F$200=G$1)) *
+ Matches!$H$2:$H$200
+)
+&amp;")"</f>
+        <v>2 (26)</v>
+      </c>
+      <c r="H32" t="str" cm="1">
+        <f t="array" ref="H32">COUNTIFS(
+ Matches!$A$2:$A$200,$A32,
+ Matches!$I$2:$I$200,"*"&amp;H$1&amp;"*"
+)
+&amp;" ("&amp;
+SUMPRODUCT(
+ (Matches!$A$2:$A$200=$A32) *
+ ((Matches!$C$2:$C$200=H$1)+(Matches!$D$2:$D$200=H$1)) *
+ Matches!$G$2:$G$200
+)
++
+SUMPRODUCT(
+ (Matches!$A$2:$A$200=$A32) *
+ ((Matches!$E$2:$E$200=H$1)+(Matches!$F$2:$F$200=H$1)) *
+ Matches!$H$2:$H$200
+)
+&amp;")"</f>
+        <v>2 (26)</v>
+      </c>
+      <c r="I32" t="str" cm="1">
+        <f t="array" ref="I32">COUNTIFS(
+ Matches!$A$2:$A$200,$A32,
+ Matches!$I$2:$I$200,"*"&amp;I$1&amp;"*"
+)
+&amp;" ("&amp;
+SUMPRODUCT(
+ (Matches!$A$2:$A$200=$A32) *
+ ((Matches!$C$2:$C$200=I$1)+(Matches!$D$2:$D$200=I$1)) *
+ Matches!$G$2:$G$200
+)
++
+SUMPRODUCT(
+ (Matches!$A$2:$A$200=$A32) *
+ ((Matches!$E$2:$E$200=I$1)+(Matches!$F$2:$F$200=I$1)) *
+ Matches!$H$2:$H$200
+)
+&amp;")"</f>
+        <v>0 (19)</v>
+      </c>
+      <c r="J32" t="s">
+        <v>101</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="F2:I31">
+  <conditionalFormatting sqref="F2:I32">
     <cfRule type="expression" dxfId="10" priority="1">
       <formula>LEFT(F2,1)="0"</formula>
     </cfRule>
@@ -3805,7 +3910,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B6F95CC-DDBC-4D0D-92B0-0E6D3AF66C09}">
-  <dimension ref="A1:K90"/>
+  <dimension ref="A1:K93"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.90625" customWidth="1"/>
@@ -3919,7 +4024,7 @@
         <v>10</v>
       </c>
       <c r="I3" t="str">
-        <f t="shared" ref="I3:I90" si="0">IF(G3&gt;H3,
+        <f t="shared" ref="I3:I93" si="0">IF(G3&gt;H3,
    IF(C3&lt;D3, C3&amp;"/"&amp;D3, D3&amp;"/"&amp;C3),
    IF(E3&lt;F3, E3&amp;"/"&amp;F3, F3&amp;"/"&amp;E3)
 )</f>
@@ -6193,7 +6298,7 @@
         <v>ML/MN</v>
       </c>
       <c r="K67" t="str">
-        <f t="shared" ref="K67:K90" si="2">_xlfn.CONCAT(A67, "-", B67)</f>
+        <f t="shared" ref="K67:K93" si="2">_xlfn.CONCAT(A67, "-", B67)</f>
         <v>R20260318-3-1</v>
       </c>
     </row>
@@ -6989,6 +7094,108 @@
       <c r="K90" t="str">
         <f t="shared" si="2"/>
         <v>R20260529-1-3</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A91" t="s">
+        <v>102</v>
+      </c>
+      <c r="B91">
+        <v>1</v>
+      </c>
+      <c r="C91" t="s">
+        <v>13</v>
+      </c>
+      <c r="D91" t="s">
+        <v>15</v>
+      </c>
+      <c r="E91" t="s">
+        <v>12</v>
+      </c>
+      <c r="F91" t="s">
+        <v>14</v>
+      </c>
+      <c r="G91" s="4">
+        <v>6</v>
+      </c>
+      <c r="H91" s="4">
+        <v>10</v>
+      </c>
+      <c r="I91" t="str">
+        <f t="shared" si="0"/>
+        <v>LX/MN</v>
+      </c>
+      <c r="K91" t="str">
+        <f t="shared" si="2"/>
+        <v>R20260725-1-1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A92" t="s">
+        <v>102</v>
+      </c>
+      <c r="B92">
+        <v>2</v>
+      </c>
+      <c r="C92" t="s">
+        <v>13</v>
+      </c>
+      <c r="D92" t="s">
+        <v>12</v>
+      </c>
+      <c r="E92" t="s">
+        <v>14</v>
+      </c>
+      <c r="F92" t="s">
+        <v>15</v>
+      </c>
+      <c r="G92" s="4">
+        <v>7</v>
+      </c>
+      <c r="H92" s="4">
+        <v>10</v>
+      </c>
+      <c r="I92" t="str">
+        <f t="shared" si="0"/>
+        <v>ML/MN</v>
+      </c>
+      <c r="K92" t="str">
+        <f t="shared" si="2"/>
+        <v>R20260725-1-2</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A93" t="s">
+        <v>102</v>
+      </c>
+      <c r="B93">
+        <v>3</v>
+      </c>
+      <c r="C93" t="s">
+        <v>14</v>
+      </c>
+      <c r="D93" t="s">
+        <v>13</v>
+      </c>
+      <c r="E93" t="s">
+        <v>12</v>
+      </c>
+      <c r="F93" t="s">
+        <v>15</v>
+      </c>
+      <c r="G93" s="4">
+        <v>6</v>
+      </c>
+      <c r="H93" s="4">
+        <v>10</v>
+      </c>
+      <c r="I93" t="str">
+        <f t="shared" si="0"/>
+        <v>LX/ML</v>
+      </c>
+      <c r="K93" t="str">
+        <f t="shared" si="2"/>
+        <v>R20260725-1-3</v>
       </c>
     </row>
   </sheetData>
@@ -8547,15 +8754,15 @@
     )
   )
 )</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" cm="1">
         <f t="array" aca="1" ref="D2" ca="1">SUMPRODUCT(--LEFT(INDIRECT("Revolutions!F2:F"&amp;$G$2)))</f>
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E2" cm="1">
         <f t="array" aca="1" ref="E2" ca="1">SUMPRODUCT(--MID(INDIRECT("Revolutions!F2:F"&amp;$G$2), FIND("(",INDIRECT("Revolutions!F2:F"&amp;$G$2))+1, LEN(INDIRECT("Revolutions!F2:F"&amp;$G$2))-FIND("(",INDIRECT("Revolutions!F2:F"&amp;$G$2))-1))</f>
-        <v>669</v>
+        <v>696</v>
       </c>
       <c r="F2" cm="1">
         <f t="array" aca="1" ref="F2" ca="1">SUM(
@@ -8571,11 +8778,11 @@
   )
  )
 )</f>
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="G2" cm="1">
         <f t="array" ref="G2">MATCH(2,1/(Revolutions!A:A&lt;&gt;""),1)</f>
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
@@ -8609,11 +8816,11 @@
       </c>
       <c r="D3" cm="1">
         <f t="array" aca="1" ref="D3" ca="1">SUMPRODUCT(--LEFT(INDIRECT("Revolutions!G2:G"&amp;$G$2),1))</f>
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E3" cm="1">
         <f t="array" aca="1" ref="E3" ca="1">SUMPRODUCT(--MID(INDIRECT("Revolutions!G2:G"&amp;$G$2), FIND("(",INDIRECT("Revolutions!G2:G"&amp;$G$2))+1, LEN(INDIRECT("Revolutions!G2:G"&amp;$G$2))-FIND("(",INDIRECT("Revolutions!G2:G"&amp;$G$2))-1))</f>
-        <v>681</v>
+        <v>707</v>
       </c>
       <c r="F3" cm="1">
         <f t="array" aca="1" ref="F3" ca="1">SUM(
@@ -8629,7 +8836,7 @@
   )
  )
 )</f>
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
@@ -8663,11 +8870,11 @@
       </c>
       <c r="D4" cm="1">
         <f t="array" aca="1" ref="D4" ca="1">SUMPRODUCT(--LEFT(INDIRECT("Revolutions!H2:H"&amp;$G$2)))</f>
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E4" cm="1">
         <f t="array" aca="1" ref="E4" ca="1">SUMPRODUCT(--MID(INDIRECT("Revolutions!H2:H"&amp;$G$2), FIND("(",INDIRECT("Revolutions!H2:H"&amp;$G$2))+1, LEN(INDIRECT("Revolutions!H2:H"&amp;$G$2))-FIND("(",INDIRECT("Revolutions!H2:H"&amp;$G$2))-1))</f>
-        <v>711</v>
+        <v>737</v>
       </c>
       <c r="F4" cm="1">
         <f t="array" aca="1" ref="F4" ca="1">SUM(
@@ -8683,7 +8890,7 @@
   )
  )
 )</f>
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
@@ -8721,7 +8928,7 @@
       </c>
       <c r="E5" cm="1">
         <f t="array" aca="1" ref="E5" ca="1">SUMPRODUCT(--MID(INDIRECT("Revolutions!I2:I"&amp;$G$2), FIND("(",INDIRECT("Revolutions!I2:I"&amp;$G$2))+1, LEN(INDIRECT("Revolutions!I2:I"&amp;$G$2))-FIND("(",INDIRECT("Revolutions!I2:I"&amp;$G$2))-1))</f>
-        <v>639</v>
+        <v>658</v>
       </c>
       <c r="F5" cm="1">
         <f t="array" aca="1" ref="F5" ca="1">SUM(
@@ -8737,7 +8944,7 @@
   )
  )
 )</f>
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
